--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -644,10 +644,10 @@
         <v>66</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.2465</v>
+        <v>0.272</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.1707</v>
+        <v>0.1812</v>
       </c>
       <c r="L2" s="5" t="n">
         <v>0.833539620209753</v>
@@ -785,7 +785,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="n">
-        <v>0.2704</v>
+        <v>0.283</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0.547516873654646</v>
@@ -867,10 +867,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0546</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.0756</v>
+        <v>0.079</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.547516873654646</v>
@@ -952,10 +952,10 @@
         <v>66</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.2374</v>
+        <v>0.265</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.3025</v>
+        <v>0.3426</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1037,10 +1037,10 @@
         <v>220</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.0688</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0243</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>0.390717855103594</v>
@@ -1116,10 +1116,10 @@
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="5" t="n">
-        <v>0.2057</v>
+        <v>0.2409</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.3181</v>
+        <v>0.3528</v>
       </c>
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
@@ -1236,10 +1236,10 @@
         <v>66</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.159</v>
+        <v>0.1687</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.1549</v>
+        <v>0.1716</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -1316,7 +1316,7 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="n">
-        <v>0.1479</v>
+        <v>0.1812</v>
       </c>
       <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
@@ -1378,10 +1378,10 @@
         <v>220</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.1081</v>
+        <v>0.1136</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.1394</v>
+        <v>0.1491</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -1513,7 +1513,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="n">
-        <v>0.3551</v>
+        <v>0.4115</v>
       </c>
       <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
@@ -1575,10 +1575,10 @@
         <v>66</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.1275</v>
+        <v>0.1415</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2606</v>
+        <v>0.3001</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1715,10 +1715,10 @@
         <v>66</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.2491</v>
+        <v>0.2739</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1566</v>
+        <v>0.1689</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.833539620209753</v>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="n">
-        <v>0.076</v>
+        <v>0.0809</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>0.390717855103594</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="5" t="n">
-        <v>0.3417</v>
+        <v>0.3914</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1950,10 +1950,10 @@
         <v>66</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.2351</v>
+        <v>0.2487</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.2256</v>
+        <v>0.241</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -2029,10 +2029,10 @@
       </c>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="5" t="n">
-        <v>0.0482</v>
+        <v>0.0488</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.0603</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
@@ -2147,10 +2147,10 @@
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="5" t="n">
-        <v>0.1906</v>
+        <v>0.2029</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.0784</v>
+        <v>0.0827</v>
       </c>
       <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
@@ -2206,10 +2206,10 @@
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="5" t="n">
-        <v>0.0316</v>
+        <v>0.0325</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="5" t="n">
-        <v>0.0284</v>
+        <v>0.0293</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0119</v>
       </c>
       <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="5" t="n">
-        <v>0.0958</v>
+        <v>0.099</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.1206</v>
+        <v>0.1302</v>
       </c>
       <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
@@ -2601,10 +2601,10 @@
       </c>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0.0678</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.1776</v>
+        <v>0.2036</v>
       </c>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
       </c>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0.125</v>
+        <v>0.1331</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.1985</v>
+        <v>0.2152</v>
       </c>
       <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="5" t="n">
-        <v>0.0467</v>
+        <v>0.0488</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.0584</v>
+        <v>0.0623</v>
       </c>
       <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
@@ -2833,10 +2833,10 @@
       </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0345</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.0324</v>
+        <v>0.0356</v>
       </c>
       <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
@@ -2893,7 +2893,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="n">
-        <v>0.2791</v>
+        <v>0.3163</v>
       </c>
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
@@ -3056,7 +3056,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="n">
-        <v>0.3008</v>
+        <v>0.3291</v>
       </c>
       <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="n">
-        <v>0.3185</v>
+        <v>0.3505</v>
       </c>
       <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
@@ -3170,7 +3170,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="n">
-        <v>0.1703</v>
+        <v>0.2154</v>
       </c>
       <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="5" t="n">
-        <v>0.1766</v>
+        <v>0.1828</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.2424</v>
+        <v>0.2573</v>
       </c>
       <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
@@ -3450,10 +3450,10 @@
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="n">
-        <v>0.173</v>
+        <v>0.1789</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.2741</v>
+        <v>0.2955</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
@@ -3509,10 +3509,10 @@
       </c>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="n">
-        <v>0.1339</v>
+        <v>0.1393</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.22</v>
+        <v>0.2357</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
@@ -3623,10 +3623,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.0847</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.0832</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.0223</v>
+        <v>0.0231</v>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="5" t="n">
-        <v>0.0498</v>
+        <v>0.0528</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.0317</v>
+        <v>0.0331</v>
       </c>
       <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
@@ -3855,10 +3855,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.2533</v>
+        <v>0.2792</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.149</v>
+        <v>0.1579</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="n">
-        <v>0.2838</v>
+        <v>0.2955</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.3998</v>
+        <v>0.4223</v>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="5" t="n">
-        <v>0.2355</v>
+        <v>0.2502</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.2821</v>
+        <v>0.3057</v>
       </c>
       <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
@@ -4032,10 +4032,10 @@
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="5" t="n">
-        <v>0.077</v>
+        <v>0.0793</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.1518</v>
+        <v>0.1657</v>
       </c>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
@@ -4091,10 +4091,10 @@
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="5" t="n">
-        <v>0.0931</v>
+        <v>0.1031</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.1385</v>
+        <v>0.1504</v>
       </c>
       <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
@@ -4150,10 +4150,10 @@
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="5" t="n">
-        <v>0.2295</v>
+        <v>0.2439</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.3559</v>
+        <v>0.3905</v>
       </c>
       <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0222</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0083</v>
       </c>
       <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="5" t="n">
-        <v>0.1581</v>
+        <v>0.1684</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>0.257</v>
+        <v>0.2925</v>
       </c>
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
@@ -4843,10 +4843,10 @@
         <v>0.9092</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.2465</v>
+        <v>0.272</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.1707</v>
+        <v>0.1812</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.833539620209753</v>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="n">
-        <v>0.2704</v>
+        <v>0.283</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.547516873654646</v>
@@ -5069,10 +5069,10 @@
         <v>0.929</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0546</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0756</v>
+        <v>0.079</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.547516873654646</v>
@@ -5153,10 +5153,10 @@
         <v>0.921</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.2374</v>
+        <v>0.265</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3025</v>
+        <v>0.3426</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -5237,10 +5237,10 @@
         <v>0.9294</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.0688</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0243</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.390717855103594</v>
@@ -5321,10 +5321,10 @@
         <v>0.9211</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2057</v>
+        <v>0.2409</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3181</v>
+        <v>0.3528</v>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
         <v>0.9051</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.159</v>
+        <v>0.1687</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1549</v>
+        <v>0.1716</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="n">
-        <v>0.1479</v>
+        <v>0.1812</v>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
@@ -5591,10 +5591,10 @@
         <v>0.8738</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.1081</v>
+        <v>0.1136</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1394</v>
+        <v>0.1491</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="n">
-        <v>0.3551</v>
+        <v>0.4115</v>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         <v>0.921</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.1275</v>
+        <v>0.1415</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2606</v>
+        <v>0.3001</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -5941,10 +5941,10 @@
         <v>0.9092</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.2491</v>
+        <v>0.2739</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1566</v>
+        <v>0.1689</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.833539620209753</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="n">
-        <v>0.076</v>
+        <v>0.0809</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0.390717855103594</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>0.3417</v>
+        <v>0.3914</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.389503957787889</v>
@@ -6173,10 +6173,10 @@
         <v>0.9051</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.2351</v>
+        <v>0.2487</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.2256</v>
+        <v>0.241</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -6257,10 +6257,10 @@
         <v>0.898</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.0482</v>
+        <v>0.0488</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.0603</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -6385,10 +6385,10 @@
         <v>0.9436</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.1906</v>
+        <v>0.2029</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0784</v>
+        <v>0.0827</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         <v>0.9436</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.0316</v>
+        <v>0.0325</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         <v>0.8868</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.0284</v>
+        <v>0.0293</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0119</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
@@ -6695,10 +6695,10 @@
         <v>0.9977</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0958</v>
+        <v>0.099</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.1206</v>
+        <v>0.1302</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -6879,10 +6879,10 @@
         <v>0.8966</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.0678</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.1776</v>
+        <v>0.2036</v>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
@@ -7003,10 +7003,10 @@
         <v>0.9827</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.125</v>
+        <v>0.1331</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.1985</v>
+        <v>0.2152</v>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -7067,10 +7067,10 @@
         <v>0.9827</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0467</v>
+        <v>0.0488</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0584</v>
+        <v>0.0623</v>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -7131,10 +7131,10 @@
         <v>0.9827</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0345</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.0324</v>
+        <v>0.0356</v>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="n">
-        <v>0.2791</v>
+        <v>0.3163</v>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="n">
-        <v>0.3008</v>
+        <v>0.3291</v>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="n">
-        <v>0.3185</v>
+        <v>0.3505</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="n">
-        <v>0.1703</v>
+        <v>0.2154</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -7679,10 +7679,10 @@
         <v>0.9822</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.1766</v>
+        <v>0.1828</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.2424</v>
+        <v>0.2573</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
         <v>0.8954</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.173</v>
+        <v>0.1789</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2741</v>
+        <v>0.2955</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.1339</v>
+        <v>0.1393</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.22</v>
+        <v>0.2357</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
@@ -7991,10 +7991,10 @@
         <v>0.9556</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.0847</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0832</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
@@ -8055,10 +8055,10 @@
         <v>0.9507</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0223</v>
+        <v>0.0231</v>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
@@ -8179,10 +8179,10 @@
         <v>0.989</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0498</v>
+        <v>0.0528</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.0317</v>
+        <v>0.0331</v>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
@@ -8243,10 +8243,10 @@
         <v>0.9556</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.2533</v>
+        <v>0.2792</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.149</v>
+        <v>0.1579</v>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
@@ -8307,10 +8307,10 @@
         <v>0.8824</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.2838</v>
+        <v>0.2955</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.3998</v>
+        <v>0.4223</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         <v>0.8824</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.2355</v>
+        <v>0.2502</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.2821</v>
+        <v>0.3057</v>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
@@ -8435,10 +8435,10 @@
         <v>0.9949</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.077</v>
+        <v>0.0793</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.1518</v>
+        <v>0.1657</v>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
@@ -8499,10 +8499,10 @@
         <v>0.983</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.0931</v>
+        <v>0.1031</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.1385</v>
+        <v>0.1504</v>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
@@ -8563,10 +8563,10 @@
         <v>0.9499</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.2295</v>
+        <v>0.2439</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.3559</v>
+        <v>0.3905</v>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
@@ -8627,10 +8627,10 @@
         <v>0.9827</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.0216</v>
+        <v>0.0222</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.0083</v>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
         <v>0.9547</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.1581</v>
+        <v>0.1684</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.257</v>
+        <v>0.2925</v>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -465,10 +465,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -482,6 +482,8 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,85 +519,95 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>REZ Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>State</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual FY24-25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Actual FY25-26</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ELI Source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -629,60 +641,70 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="K2" s="5" t="n">
         <v>0.272</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2" s="5" t="n">
         <v>0.1812</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
-      <c r="M2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>0.8986</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="Q2" s="5" t="n">
         <v>0.9092</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="R2" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q2" s="6" t="n">
+      <c r="S2" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="T2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="U2" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U2" s="6" t="n">
+      <c r="W2" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V2" s="6" t="n">
+      <c r="X2" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W2" s="6" t="n">
+      <c r="Y2" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -703,43 +725,37 @@
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>186</v>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="5" t="n">
         <v>0.8883</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="Q3" s="5" t="n">
         <v>0.8963</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
+      <c r="Y3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -769,58 +785,68 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>31.16</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="n">
         <v>0.283</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="n">
         <v>0.9305</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="R4" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="S4" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="T4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="U4" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="V4" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U4" s="6" t="n">
+      <c r="W4" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W4" s="6" t="n">
+      <c r="Y4" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -852,60 +878,70 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>0.0546</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>0.079</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.547516873654646</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.122422882740379</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
         <v>0.9305</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="S5" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="T5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="U5" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="V5" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="Y5" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -942,38 +978,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>93.48</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>0.265</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="L6" s="5" t="n">
         <v>0.3426</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="Q6" s="5" t="n">
         <v>0.921</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
@@ -982,17 +1022,23 @@
         <v>0</v>
       </c>
       <c r="T6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V6" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="W6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="X6" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1027,38 +1073,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="J7" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>0.07920000000000001</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>0.0243</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="N7" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
         <v>0.949</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="Q7" s="5" t="n">
         <v>0.9294</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
         <v>0</v>
@@ -1067,17 +1117,23 @@
         <v>0</v>
       </c>
       <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V7" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="W7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="X7" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1096,47 +1152,41 @@
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
         <v>0.2409</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="L8" s="5" t="n">
         <v>0.3528</v>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="n">
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="5" t="n">
         <v>0.9402</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="Q8" s="5" t="n">
         <v>0.9211</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="6" t="inlineStr"/>
       <c r="U8" s="6" t="inlineStr"/>
       <c r="V8" s="6" t="inlineStr"/>
       <c r="W8" s="6" t="inlineStr"/>
+      <c r="X8" s="6" t="inlineStr"/>
+      <c r="Y8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1155,43 +1205,37 @@
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>348.6</v>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="n">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="5" t="n">
         <v>0.9328</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="Q9" s="5" t="n">
         <v>0.9261</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="6" t="inlineStr"/>
       <c r="T9" s="6" t="inlineStr"/>
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="6" t="inlineStr"/>
+      <c r="X9" s="6" t="inlineStr"/>
+      <c r="Y9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1221,60 +1265,70 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>104.5</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>0.1687</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>0.1716</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
         <v>0.8895</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="Q10" s="5" t="n">
         <v>0.9051</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="R10" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q10" s="6" t="n">
+      <c r="S10" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="T10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="U10" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="V10" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="W10" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W10" s="6" t="n">
+      <c r="Y10" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1295,45 +1349,39 @@
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="n">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
         <v>0.1812</v>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="n">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="5" t="n">
         <v>0.9329</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="Q11" s="5" t="n">
         <v>0.9311</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="6" t="inlineStr"/>
       <c r="T11" s="6" t="inlineStr"/>
       <c r="U11" s="6" t="inlineStr"/>
       <c r="V11" s="6" t="inlineStr"/>
       <c r="W11" s="6" t="inlineStr"/>
+      <c r="X11" s="6" t="inlineStr"/>
+      <c r="Y11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1363,60 +1411,70 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>199.95</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>0.1136</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>0.1491</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>0.827440107601162</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.0878331516592939</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
         <v>0.8784999999999999</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="Q12" s="5" t="n">
         <v>0.8738</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="R12" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="S12" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="T12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="U12" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="V12" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="W12" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="X12" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="Y12" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1437,43 +1495,37 @@
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="n">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="5" t="n">
         <v>0.9441000000000001</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="Q13" s="5" t="n">
         <v>0.921</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="6" t="inlineStr"/>
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="6" t="inlineStr"/>
       <c r="V13" s="6" t="inlineStr"/>
       <c r="W13" s="6" t="inlineStr"/>
+      <c r="X13" s="6" t="inlineStr"/>
+      <c r="Y13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1492,45 +1544,39 @@
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="5" t="n">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
         <v>0.4115</v>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="n">
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="5" t="n">
         <v>0.9415</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="Q14" s="5" t="n">
         <v>0.9257</v>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="6" t="inlineStr"/>
       <c r="T14" s="6" t="inlineStr"/>
       <c r="U14" s="6" t="inlineStr"/>
       <c r="V14" s="6" t="inlineStr"/>
       <c r="W14" s="6" t="inlineStr"/>
+      <c r="X14" s="6" t="inlineStr"/>
+      <c r="Y14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1565,38 +1611,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>101.08</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="K15" s="5" t="n">
         <v>0.1415</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>0.3001</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="Q15" s="5" t="n">
         <v>0.921</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
         <v>0</v>
@@ -1605,17 +1655,23 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="W15" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="X15" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1634,43 +1690,37 @@
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="n">
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="Q16" s="5" t="n">
         <v>0.9282</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="6" t="inlineStr"/>
       <c r="T16" s="6" t="inlineStr"/>
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1700,60 +1750,70 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="K17" s="5" t="n">
         <v>0.2739</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>0.1689</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.833539620209753</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.164192244302687</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>0.8986</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="Q17" s="5" t="n">
         <v>0.9092</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="R17" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="S17" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="T17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="U17" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="V17" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="W17" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="X17" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="Y17" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1790,36 +1850,40 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="J18" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="n">
+      <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="n">
         <v>0.0809</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>0.390717855103594</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>0.08997768712489811</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
         <v>0.9402</v>
       </c>
-      <c r="O18" s="5" t="n">
+      <c r="Q18" s="5" t="n">
         <v>0.9211</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>0</v>
@@ -1828,17 +1892,23 @@
         <v>0</v>
       </c>
       <c r="T18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="6" t="n">
         <v>0.04</v>
-      </c>
-      <c r="U18" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V18" s="6" t="n">
-        <v>0.1</v>
       </c>
       <c r="W18" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="X18" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1873,39 +1943,49 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>93.5</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="5" t="n">
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="n">
         <v>0.3914</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.389503957787889</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.08205629867681941</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="Q19" s="5" t="n">
         <v>0.921</v>
       </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="6" t="inlineStr"/>
       <c r="R19" s="6" t="inlineStr"/>
       <c r="S19" s="6" t="inlineStr"/>
       <c r="T19" s="6" t="inlineStr"/>
       <c r="U19" s="6" t="inlineStr"/>
       <c r="V19" s="6" t="inlineStr"/>
       <c r="W19" s="6" t="inlineStr"/>
+      <c r="X19" s="6" t="inlineStr"/>
+      <c r="Y19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1935,60 +2015,70 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murray River </t>
+          <t>Murray River</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>0.2487</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>0.241</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.8554020168196</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.072415601225557</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>0.8895</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="Q20" s="5" t="n">
         <v>0.9051</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="R20" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="S20" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="T20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="U20" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="V20" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="W20" s="6" t="n">
         <v>0.17</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="X20" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="Y20" s="6" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -2009,47 +2099,41 @@
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>241.59</v>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="5" t="n">
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="5" t="n">
         <v>0.0488</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="n">
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="5" t="n">
         <v>0.9031</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="Q21" s="5" t="n">
         <v>0.898</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr"/>
       <c r="S21" s="6" t="inlineStr"/>
       <c r="T21" s="6" t="inlineStr"/>
       <c r="U21" s="6" t="inlineStr"/>
       <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="6" t="inlineStr"/>
+      <c r="X21" s="6" t="inlineStr"/>
+      <c r="Y21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2068,47 +2152,41 @@
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="I22" s="4" t="n">
         <v>106.6</v>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
         <v>0.0051</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="L22" s="5" t="n">
         <v>0.003</v>
       </c>
-      <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="n">
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="Q22" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
+      <c r="Y22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2127,47 +2205,41 @@
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="I23" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
         <v>0.2029</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.0827</v>
       </c>
-      <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="n">
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="5" t="n">
         <v>0.9465</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="Q23" s="5" t="n">
         <v>0.9436</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
       <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="inlineStr"/>
       <c r="U23" s="6" t="inlineStr"/>
       <c r="V23" s="6" t="inlineStr"/>
       <c r="W23" s="6" t="inlineStr"/>
+      <c r="X23" s="6" t="inlineStr"/>
+      <c r="Y23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2186,47 +2258,41 @@
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>180.6</v>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
         <v>0.0325</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>0.016</v>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="n">
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="5" t="n">
         <v>0.9465</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="Q24" s="5" t="n">
         <v>0.9436</v>
       </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
       <c r="S24" s="6" t="inlineStr"/>
       <c r="T24" s="6" t="inlineStr"/>
       <c r="U24" s="6" t="inlineStr"/>
       <c r="V24" s="6" t="inlineStr"/>
       <c r="W24" s="6" t="inlineStr"/>
+      <c r="X24" s="6" t="inlineStr"/>
+      <c r="Y24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2245,47 +2311,41 @@
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
         <v>0.0293</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="L25" s="5" t="n">
         <v>0.0119</v>
       </c>
-      <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="n">
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="5" t="n">
         <v>0.8907</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="Q25" s="5" t="n">
         <v>0.8868</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
+      <c r="Y25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2304,43 +2364,37 @@
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>52.5</v>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="n">
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="Q26" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="6" t="inlineStr"/>
       <c r="R26" s="6" t="inlineStr"/>
       <c r="S26" s="6" t="inlineStr"/>
       <c r="T26" s="6" t="inlineStr"/>
       <c r="U26" s="6" t="inlineStr"/>
       <c r="V26" s="6" t="inlineStr"/>
       <c r="W26" s="6" t="inlineStr"/>
+      <c r="X26" s="6" t="inlineStr"/>
+      <c r="Y26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2359,41 +2413,35 @@
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>6.15</v>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="n">
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
+      <c r="Y27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2412,47 +2460,41 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>57.6</v>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="5" t="n">
         <v>0.099</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>0.1302</v>
       </c>
-      <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="n">
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="5" t="n">
         <v>0.998</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>0.9977</v>
       </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr"/>
       <c r="S28" s="6" t="inlineStr"/>
       <c r="T28" s="6" t="inlineStr"/>
       <c r="U28" s="6" t="inlineStr"/>
       <c r="V28" s="6" t="inlineStr"/>
       <c r="W28" s="6" t="inlineStr"/>
+      <c r="X28" s="6" t="inlineStr"/>
+      <c r="Y28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2471,43 +2513,37 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="n">
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="Q29" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
+      <c r="Y29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2526,43 +2562,37 @@
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>19.8</v>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="n">
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="5" t="n">
         <v>1.0166</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="Q30" s="5" t="n">
         <v>1.0031</v>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
-      <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr"/>
       <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="6" t="inlineStr"/>
       <c r="U30" s="6" t="inlineStr"/>
       <c r="V30" s="6" t="inlineStr"/>
       <c r="W30" s="6" t="inlineStr"/>
+      <c r="X30" s="6" t="inlineStr"/>
+      <c r="Y30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2581,47 +2611,41 @@
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>79.95</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="5" t="n">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="5" t="n">
         <v>0.07679999999999999</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="L31" s="5" t="n">
         <v>0.2036</v>
       </c>
-      <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="n">
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="5" t="n">
         <v>0.9004</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="Q31" s="5" t="n">
         <v>0.8966</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
+      <c r="Y31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2640,43 +2664,37 @@
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="n">
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="5" t="n">
         <v>0.8959</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="Q32" s="5" t="n">
         <v>0.8954</v>
       </c>
-      <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="6" t="inlineStr"/>
       <c r="R32" s="6" t="inlineStr"/>
       <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr"/>
       <c r="W32" s="6" t="inlineStr"/>
+      <c r="X32" s="6" t="inlineStr"/>
+      <c r="Y32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2695,47 +2713,41 @@
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="5" t="n">
         <v>0.1331</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="L33" s="5" t="n">
         <v>0.2152</v>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="n">
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="Q33" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr"/>
       <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="inlineStr"/>
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr"/>
       <c r="W33" s="6" t="inlineStr"/>
+      <c r="X33" s="6" t="inlineStr"/>
+      <c r="Y33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2754,47 +2766,41 @@
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="5" t="n">
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="5" t="n">
         <v>0.0488</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="L34" s="5" t="n">
         <v>0.0623</v>
       </c>
-      <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="n">
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="Q34" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr"/>
       <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="inlineStr"/>
       <c r="U34" s="6" t="inlineStr"/>
       <c r="V34" s="6" t="inlineStr"/>
       <c r="W34" s="6" t="inlineStr"/>
+      <c r="X34" s="6" t="inlineStr"/>
+      <c r="Y34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2813,47 +2819,41 @@
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="5" t="n">
         <v>0.0345</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>0.0356</v>
       </c>
-      <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="n">
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="Q35" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="6" t="inlineStr"/>
       <c r="R35" s="6" t="inlineStr"/>
       <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="6" t="inlineStr"/>
       <c r="U35" s="6" t="inlineStr"/>
       <c r="V35" s="6" t="inlineStr"/>
       <c r="W35" s="6" t="inlineStr"/>
+      <c r="X35" s="6" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2872,45 +2872,39 @@
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="I36" s="4" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="n">
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="n">
         <v>0.3163</v>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="n">
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="Q36" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr"/>
       <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="6" t="inlineStr"/>
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr"/>
       <c r="W36" s="6" t="inlineStr"/>
+      <c r="X36" s="6" t="inlineStr"/>
+      <c r="Y36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2929,39 +2923,33 @@
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
       <c r="N37" s="5" t="inlineStr"/>
-      <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="6" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr"/>
       <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" s="6" t="inlineStr"/>
       <c r="V37" s="6" t="inlineStr"/>
       <c r="W37" s="6" t="inlineStr"/>
+      <c r="X37" s="6" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2980,43 +2968,37 @@
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
       <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="n">
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="O38" s="5" t="n">
+      <c r="Q38" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
+      <c r="Y38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3035,45 +3017,39 @@
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="n">
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="n">
         <v>0.3291</v>
       </c>
-      <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="n">
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="O39" s="5" t="n">
+      <c r="Q39" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr"/>
       <c r="S39" s="6" t="inlineStr"/>
       <c r="T39" s="6" t="inlineStr"/>
       <c r="U39" s="6" t="inlineStr"/>
       <c r="V39" s="6" t="inlineStr"/>
       <c r="W39" s="6" t="inlineStr"/>
+      <c r="X39" s="6" t="inlineStr"/>
+      <c r="Y39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3092,45 +3068,39 @@
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="I40" s="4" t="n">
         <v>260.4</v>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="n">
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="n">
         <v>0.3505</v>
       </c>
-      <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="n">
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="O40" s="5" t="n">
+      <c r="Q40" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="6" t="inlineStr"/>
       <c r="R40" s="6" t="inlineStr"/>
       <c r="S40" s="6" t="inlineStr"/>
       <c r="T40" s="6" t="inlineStr"/>
       <c r="U40" s="6" t="inlineStr"/>
       <c r="V40" s="6" t="inlineStr"/>
       <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
+      <c r="Y40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3149,45 +3119,39 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="I41" s="4" t="n">
         <v>248</v>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="n">
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="n">
         <v>0.2154</v>
       </c>
-      <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="n">
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="5" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="Q41" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr"/>
       <c r="S41" s="6" t="inlineStr"/>
       <c r="T41" s="6" t="inlineStr"/>
       <c r="U41" s="6" t="inlineStr"/>
       <c r="V41" s="6" t="inlineStr"/>
       <c r="W41" s="6" t="inlineStr"/>
+      <c r="X41" s="6" t="inlineStr"/>
+      <c r="Y41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3206,43 +3170,37 @@
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>266</v>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="n">
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="O42" s="5" t="n">
+      <c r="Q42" s="5" t="n">
         <v>0.9823</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="6" t="inlineStr"/>
       <c r="R42" s="6" t="inlineStr"/>
       <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="inlineStr"/>
       <c r="U42" s="6" t="inlineStr"/>
       <c r="V42" s="6" t="inlineStr"/>
       <c r="W42" s="6" t="inlineStr"/>
+      <c r="X42" s="6" t="inlineStr"/>
+      <c r="Y42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3261,43 +3219,37 @@
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>310</v>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="n">
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="5" t="n">
         <v>0.9837</v>
       </c>
-      <c r="O43" s="5" t="n">
+      <c r="Q43" s="5" t="n">
         <v>0.9823</v>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="6" t="inlineStr"/>
       <c r="R43" s="6" t="inlineStr"/>
       <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="6" t="inlineStr"/>
       <c r="U43" s="6" t="inlineStr"/>
       <c r="V43" s="6" t="inlineStr"/>
       <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
+      <c r="Y43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3316,47 +3268,41 @@
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="I44" s="4" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="n">
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="5" t="n">
         <v>0.1828</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="L44" s="5" t="n">
         <v>0.2573</v>
       </c>
-      <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="n">
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="5" t="n">
         <v>0.9865</v>
       </c>
-      <c r="O44" s="5" t="n">
+      <c r="Q44" s="5" t="n">
         <v>0.9822</v>
       </c>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" s="6" t="inlineStr"/>
       <c r="R44" s="6" t="inlineStr"/>
       <c r="S44" s="6" t="inlineStr"/>
       <c r="T44" s="6" t="inlineStr"/>
       <c r="U44" s="6" t="inlineStr"/>
       <c r="V44" s="6" t="inlineStr"/>
       <c r="W44" s="6" t="inlineStr"/>
+      <c r="X44" s="6" t="inlineStr"/>
+      <c r="Y44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3375,43 +3321,37 @@
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr"/>
       <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="n">
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="O45" s="5" t="n">
+      <c r="Q45" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="6" t="inlineStr"/>
       <c r="R45" s="6" t="inlineStr"/>
       <c r="S45" s="6" t="inlineStr"/>
       <c r="T45" s="6" t="inlineStr"/>
       <c r="U45" s="6" t="inlineStr"/>
       <c r="V45" s="6" t="inlineStr"/>
       <c r="W45" s="6" t="inlineStr"/>
+      <c r="X45" s="6" t="inlineStr"/>
+      <c r="Y45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3430,47 +3370,41 @@
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="I46" s="4" t="n">
         <v>31.05</v>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="5" t="n">
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
         <v>0.1789</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="L46" s="5" t="n">
         <v>0.2955</v>
       </c>
-      <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="n">
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="5" t="n">
         <v>0.8959</v>
       </c>
-      <c r="O46" s="5" t="n">
+      <c r="Q46" s="5" t="n">
         <v>0.8954</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
       <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="inlineStr"/>
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr"/>
       <c r="W46" s="6" t="inlineStr"/>
+      <c r="X46" s="6" t="inlineStr"/>
+      <c r="Y46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3489,47 +3423,41 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H47" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="5" t="n">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="5" t="n">
         <v>0.1393</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="L47" s="5" t="n">
         <v>0.2357</v>
       </c>
-      <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="n">
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="5" t="n">
         <v>0.9829</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="Q47" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
+      <c r="Y47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3548,43 +3476,37 @@
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H48" s="4" t="n">
+      <c r="I48" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="n">
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="O48" s="5" t="n">
+      <c r="Q48" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
+      <c r="Y48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3603,47 +3525,41 @@
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H49" s="4" t="n">
+      <c r="I49" s="4" t="n">
         <v>312</v>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="5" t="n">
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="5" t="n">
         <v>0.09030000000000001</v>
       </c>
-      <c r="K49" s="5" t="n">
+      <c r="L49" s="5" t="n">
         <v>0.08890000000000001</v>
       </c>
-      <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="n">
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="O49" s="5" t="n">
+      <c r="Q49" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
-      <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
+      <c r="Y49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3662,47 +3578,41 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="I50" s="4" t="n">
         <v>157.5</v>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="5" t="n">
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="5" t="n">
         <v>0.106</v>
       </c>
-      <c r="K50" s="5" t="n">
+      <c r="L50" s="5" t="n">
         <v>0.0231</v>
       </c>
-      <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="n">
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="5" t="n">
         <v>0.9525</v>
       </c>
-      <c r="O50" s="5" t="n">
+      <c r="Q50" s="5" t="n">
         <v>0.9507</v>
       </c>
-      <c r="P50" s="6" t="inlineStr"/>
-      <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="6" t="inlineStr"/>
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
+      <c r="Y50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3721,43 +3631,37 @@
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="n">
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="O51" s="5" t="n">
+      <c r="Q51" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
+      <c r="Y51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3776,47 +3680,41 @@
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="I52" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="5" t="n">
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="5" t="n">
         <v>0.0528</v>
       </c>
-      <c r="K52" s="5" t="n">
+      <c r="L52" s="5" t="n">
         <v>0.0331</v>
       </c>
-      <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="n">
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="5" t="n">
         <v>0.9879</v>
       </c>
-      <c r="O52" s="5" t="n">
+      <c r="Q52" s="5" t="n">
         <v>0.989</v>
       </c>
-      <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="6" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
+      <c r="Y52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3835,47 +3733,41 @@
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="I53" s="4" t="n">
         <v>131.2</v>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="5" t="n">
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="5" t="n">
         <v>0.2792</v>
       </c>
-      <c r="K53" s="5" t="n">
+      <c r="L53" s="5" t="n">
         <v>0.1579</v>
       </c>
-      <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="n">
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="5" t="n">
         <v>0.9569</v>
       </c>
-      <c r="O53" s="5" t="n">
+      <c r="Q53" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="P53" s="6" t="inlineStr"/>
-      <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="6" t="inlineStr"/>
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
+      <c r="Y53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3894,47 +3786,41 @@
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="I54" s="4" t="n">
         <v>231.8</v>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="5" t="n">
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="5" t="n">
         <v>0.2955</v>
       </c>
-      <c r="K54" s="5" t="n">
+      <c r="L54" s="5" t="n">
         <v>0.4223</v>
       </c>
-      <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="n">
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="5" t="n">
         <v>0.8817</v>
       </c>
-      <c r="O54" s="5" t="n">
+      <c r="Q54" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="6" t="inlineStr"/>
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
+      <c r="Y54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3953,47 +3839,41 @@
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>209</v>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="5" t="n">
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="5" t="n">
         <v>0.2502</v>
       </c>
-      <c r="K55" s="5" t="n">
+      <c r="L55" s="5" t="n">
         <v>0.3057</v>
       </c>
-      <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="n">
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="5" t="n">
         <v>0.8817</v>
       </c>
-      <c r="O55" s="5" t="n">
+      <c r="Q55" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="6" t="inlineStr"/>
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
+      <c r="Y55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4012,47 +3892,41 @@
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="I56" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="5" t="n">
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="5" t="n">
         <v>0.0793</v>
       </c>
-      <c r="K56" s="5" t="n">
+      <c r="L56" s="5" t="n">
         <v>0.1657</v>
       </c>
-      <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="n">
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="O56" s="5" t="n">
+      <c r="Q56" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P56" s="6" t="inlineStr"/>
-      <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="6" t="inlineStr"/>
       <c r="S56" s="6" t="inlineStr"/>
       <c r="T56" s="6" t="inlineStr"/>
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
+      <c r="Y56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4071,47 +3945,41 @@
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>218.4</v>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="5" t="n">
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="5" t="n">
         <v>0.1031</v>
       </c>
-      <c r="K57" s="5" t="n">
+      <c r="L57" s="5" t="n">
         <v>0.1504</v>
       </c>
-      <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="n">
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="5" t="n">
         <v>0.9875</v>
       </c>
-      <c r="O57" s="5" t="n">
+      <c r="Q57" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
-      <c r="Q57" s="6" t="inlineStr"/>
       <c r="R57" s="6" t="inlineStr"/>
       <c r="S57" s="6" t="inlineStr"/>
       <c r="T57" s="6" t="inlineStr"/>
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr"/>
       <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
+      <c r="Y57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4130,47 +3998,41 @@
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="I58" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="5" t="n">
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="5" t="n">
         <v>0.2439</v>
       </c>
-      <c r="K58" s="5" t="n">
+      <c r="L58" s="5" t="n">
         <v>0.3905</v>
       </c>
-      <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="5" t="n">
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="5" t="n">
         <v>0.9519</v>
       </c>
-      <c r="O58" s="5" t="n">
+      <c r="Q58" s="5" t="n">
         <v>0.9499</v>
       </c>
-      <c r="P58" s="6" t="inlineStr"/>
-      <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="6" t="inlineStr"/>
       <c r="S58" s="6" t="inlineStr"/>
       <c r="T58" s="6" t="inlineStr"/>
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr"/>
       <c r="W58" s="6" t="inlineStr"/>
+      <c r="X58" s="6" t="inlineStr"/>
+      <c r="Y58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4189,47 +4051,41 @@
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="I59" s="4" t="n">
         <v>531</v>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="5" t="n">
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="5" t="n">
         <v>0.0222</v>
       </c>
-      <c r="K59" s="5" t="n">
+      <c r="L59" s="5" t="n">
         <v>0.0083</v>
       </c>
-      <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="n">
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="5" t="n">
         <v>0.9845</v>
       </c>
-      <c r="O59" s="5" t="n">
+      <c r="Q59" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P59" s="6" t="inlineStr"/>
-      <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="6" t="inlineStr"/>
       <c r="S59" s="6" t="inlineStr"/>
       <c r="T59" s="6" t="inlineStr"/>
       <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr"/>
       <c r="W59" s="6" t="inlineStr"/>
+      <c r="X59" s="6" t="inlineStr"/>
+      <c r="Y59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4248,43 +4104,37 @@
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H60" s="4" t="n">
+      <c r="I60" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr"/>
       <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
-      <c r="N60" s="5" t="n">
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="O60" s="5" t="n">
+      <c r="Q60" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P60" s="6" t="inlineStr"/>
-      <c r="Q60" s="6" t="inlineStr"/>
       <c r="R60" s="6" t="inlineStr"/>
       <c r="S60" s="6" t="inlineStr"/>
       <c r="T60" s="6" t="inlineStr"/>
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr"/>
       <c r="W60" s="6" t="inlineStr"/>
+      <c r="X60" s="6" t="inlineStr"/>
+      <c r="Y60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4303,43 +4153,37 @@
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H61" s="4" t="n">
+      <c r="I61" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="5" t="inlineStr"/>
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
-      <c r="N61" s="5" t="n">
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="O61" s="5" t="n">
+      <c r="Q61" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P61" s="6" t="inlineStr"/>
-      <c r="Q61" s="6" t="inlineStr"/>
       <c r="R61" s="6" t="inlineStr"/>
       <c r="S61" s="6" t="inlineStr"/>
       <c r="T61" s="6" t="inlineStr"/>
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr"/>
       <c r="W61" s="6" t="inlineStr"/>
+      <c r="X61" s="6" t="inlineStr"/>
+      <c r="Y61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4358,43 +4202,37 @@
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
-      <c r="N62" s="5" t="n">
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="5" t="n">
         <v>0.9329</v>
       </c>
-      <c r="O62" s="5" t="n">
+      <c r="Q62" s="5" t="n">
         <v>0.9298999999999999</v>
       </c>
-      <c r="P62" s="6" t="inlineStr"/>
-      <c r="Q62" s="6" t="inlineStr"/>
       <c r="R62" s="6" t="inlineStr"/>
       <c r="S62" s="6" t="inlineStr"/>
       <c r="T62" s="6" t="inlineStr"/>
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr"/>
       <c r="W62" s="6" t="inlineStr"/>
+      <c r="X62" s="6" t="inlineStr"/>
+      <c r="Y62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4413,43 +4251,37 @@
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="I63" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr"/>
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
-      <c r="N63" s="5" t="n">
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="5" t="n">
         <v>0.9862</v>
       </c>
-      <c r="O63" s="5" t="n">
+      <c r="Q63" s="5" t="n">
         <v>0.992</v>
       </c>
-      <c r="P63" s="6" t="inlineStr"/>
-      <c r="Q63" s="6" t="inlineStr"/>
       <c r="R63" s="6" t="inlineStr"/>
       <c r="S63" s="6" t="inlineStr"/>
       <c r="T63" s="6" t="inlineStr"/>
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr"/>
       <c r="W63" s="6" t="inlineStr"/>
+      <c r="X63" s="6" t="inlineStr"/>
+      <c r="Y63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4468,43 +4300,37 @@
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H64" s="4" t="n">
+      <c r="I64" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr"/>
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
-      <c r="N64" s="5" t="n">
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="5" t="n">
         <v>0.9825</v>
       </c>
-      <c r="O64" s="5" t="n">
+      <c r="Q64" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P64" s="6" t="inlineStr"/>
-      <c r="Q64" s="6" t="inlineStr"/>
       <c r="R64" s="6" t="inlineStr"/>
       <c r="S64" s="6" t="inlineStr"/>
       <c r="T64" s="6" t="inlineStr"/>
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr"/>
       <c r="W64" s="6" t="inlineStr"/>
+      <c r="X64" s="6" t="inlineStr"/>
+      <c r="Y64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4523,43 +4349,37 @@
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="I65" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="5" t="inlineStr"/>
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
-      <c r="N65" s="5" t="n">
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="5" t="n">
         <v>1.0018</v>
       </c>
-      <c r="O65" s="5" t="n">
+      <c r="Q65" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="P65" s="6" t="inlineStr"/>
-      <c r="Q65" s="6" t="inlineStr"/>
       <c r="R65" s="6" t="inlineStr"/>
       <c r="S65" s="6" t="inlineStr"/>
       <c r="T65" s="6" t="inlineStr"/>
       <c r="U65" s="6" t="inlineStr"/>
       <c r="V65" s="6" t="inlineStr"/>
       <c r="W65" s="6" t="inlineStr"/>
+      <c r="X65" s="6" t="inlineStr"/>
+      <c r="Y65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4578,43 +4398,37 @@
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="I66" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr"/>
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
-      <c r="N66" s="5" t="n">
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="5" t="n">
         <v>1.0166</v>
       </c>
-      <c r="O66" s="5" t="n">
+      <c r="Q66" s="5" t="n">
         <v>1.0031</v>
       </c>
-      <c r="P66" s="6" t="inlineStr"/>
-      <c r="Q66" s="6" t="inlineStr"/>
       <c r="R66" s="6" t="inlineStr"/>
       <c r="S66" s="6" t="inlineStr"/>
       <c r="T66" s="6" t="inlineStr"/>
       <c r="U66" s="6" t="inlineStr"/>
       <c r="V66" s="6" t="inlineStr"/>
       <c r="W66" s="6" t="inlineStr"/>
+      <c r="X66" s="6" t="inlineStr"/>
+      <c r="Y66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4633,47 +4447,41 @@
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="H67" s="4" t="n">
+      <c r="I67" s="4" t="n">
         <v>144.4</v>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="5" t="n">
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="5" t="n">
         <v>0.1684</v>
       </c>
-      <c r="K67" s="5" t="n">
+      <c r="L67" s="5" t="n">
         <v>0.2925</v>
       </c>
-      <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="5" t="n">
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="5" t="n">
         <v>0.9537</v>
       </c>
-      <c r="O67" s="5" t="n">
+      <c r="Q67" s="5" t="n">
         <v>0.9547</v>
       </c>
-      <c r="P67" s="6" t="inlineStr"/>
-      <c r="Q67" s="6" t="inlineStr"/>
       <c r="R67" s="6" t="inlineStr"/>
       <c r="S67" s="6" t="inlineStr"/>
       <c r="T67" s="6" t="inlineStr"/>
       <c r="U67" s="6" t="inlineStr"/>
       <c r="V67" s="6" t="inlineStr"/>
       <c r="W67" s="6" t="inlineStr"/>
+      <c r="X67" s="6" t="inlineStr"/>
+      <c r="Y67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4931,42 +4739,18 @@
       <c r="G3" s="5" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -5329,42 +5113,18 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
       <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S8" s="5" t="inlineStr"/>
       <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U8" s="5" t="inlineStr"/>
       <c r="V8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -5389,42 +5149,18 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L9" s="5" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
       <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S9" s="5" t="inlineStr"/>
       <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -5535,42 +5271,18 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L11" s="5" t="inlineStr"/>
       <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N11" s="5" t="inlineStr"/>
       <c r="O11" s="5" t="inlineStr"/>
       <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr"/>
-      <c r="S11" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U11" s="5" t="inlineStr"/>
       <c r="V11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
@@ -5679,42 +5391,18 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L13" s="5" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N13" s="5" t="inlineStr"/>
       <c r="O13" s="5" t="inlineStr"/>
       <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="inlineStr"/>
-      <c r="S13" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S13" s="5" t="inlineStr"/>
       <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U13" s="5" t="inlineStr"/>
       <c r="V13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
@@ -5741,42 +5429,18 @@
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L14" s="5" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N14" s="5" t="inlineStr"/>
       <c r="O14" s="5" t="inlineStr"/>
       <c r="P14" s="5" t="inlineStr"/>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr"/>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S14" s="5" t="inlineStr"/>
       <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U14" s="5" t="inlineStr"/>
       <c r="V14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
@@ -5885,42 +5549,18 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S16" s="5" t="inlineStr"/>
       <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
@@ -6265,42 +5905,18 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L21" s="5" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q21" s="5" t="inlineStr"/>
       <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S21" s="5" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -6329,42 +5945,18 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -6393,42 +5985,18 @@
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L23" s="5" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q23" s="5" t="inlineStr"/>
       <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S23" s="5" t="inlineStr"/>
       <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U23" s="5" t="inlineStr"/>
       <c r="V23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -6457,42 +6025,18 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
       <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q24" s="5" t="inlineStr"/>
       <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U24" s="5" t="inlineStr"/>
       <c r="V24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -6521,42 +6065,18 @@
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
@@ -6581,42 +6101,18 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L26" s="5" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
       <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q26" s="5" t="inlineStr"/>
       <c r="R26" s="5" t="inlineStr"/>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
@@ -6639,42 +6135,18 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
@@ -6703,42 +6175,18 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L28" s="5" t="inlineStr"/>
       <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr"/>
       <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q28" s="5" t="inlineStr"/>
       <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
@@ -6763,42 +6211,18 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -6823,42 +6247,18 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L30" s="5" t="inlineStr"/>
       <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
       <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q30" s="5" t="inlineStr"/>
       <c r="R30" s="5" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S30" s="5" t="inlineStr"/>
       <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
@@ -6887,42 +6287,18 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
@@ -6947,42 +6323,18 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L32" s="5" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="5" t="inlineStr"/>
       <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q32" s="5" t="inlineStr"/>
       <c r="R32" s="5" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S32" s="5" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr"/>
-      <c r="U32" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
@@ -7011,42 +6363,18 @@
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L33" s="5" t="inlineStr"/>
       <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="5" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q33" s="5" t="inlineStr"/>
       <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S33" s="5" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U33" s="5" t="inlineStr"/>
       <c r="V33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
@@ -7075,42 +6403,18 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L34" s="5" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
       <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q34" s="5" t="inlineStr"/>
       <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S34" s="5" t="inlineStr"/>
       <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U34" s="5" t="inlineStr"/>
       <c r="V34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
@@ -7139,42 +6443,18 @@
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L35" s="5" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr"/>
       <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q35" s="5" t="inlineStr"/>
       <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S35" s="5" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U35" s="5" t="inlineStr"/>
       <c r="V35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
@@ -7201,42 +6481,18 @@
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N36" s="5" t="inlineStr"/>
       <c r="O36" s="5" t="inlineStr"/>
       <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q36" s="5" t="inlineStr"/>
       <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S36" s="5" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U36" s="5" t="inlineStr"/>
       <c r="V36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
@@ -7257,42 +6513,18 @@
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J37" s="5" t="inlineStr"/>
       <c r="K37" s="5" t="inlineStr"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L37" s="5" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr"/>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q37" s="5" t="inlineStr"/>
       <c r="R37" s="5" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S37" s="5" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr"/>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
@@ -7317,42 +6549,18 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
@@ -7379,42 +6587,18 @@
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J39" s="5" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L39" s="5" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N39" s="5" t="inlineStr"/>
       <c r="O39" s="5" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q39" s="5" t="inlineStr"/>
       <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S39" s="5" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
@@ -7441,42 +6625,18 @@
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L40" s="5" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="5" t="inlineStr"/>
       <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q40" s="5" t="inlineStr"/>
       <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S40" s="5" t="inlineStr"/>
       <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
@@ -7503,42 +6663,18 @@
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J41" s="5" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L41" s="5" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
       <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q41" s="5" t="inlineStr"/>
       <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S41" s="5" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U41" s="5" t="inlineStr"/>
       <c r="V41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
@@ -7563,42 +6699,18 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="inlineStr"/>
       <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q42" s="5" t="inlineStr"/>
       <c r="R42" s="5" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S42" s="5" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr"/>
-      <c r="U42" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U42" s="5" t="inlineStr"/>
       <c r="V42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
@@ -7623,42 +6735,18 @@
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J43" s="5" t="inlineStr"/>
       <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L43" s="5" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="5" t="inlineStr"/>
       <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q43" s="5" t="inlineStr"/>
       <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S43" s="5" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
@@ -7687,42 +6775,18 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L44" s="5" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N44" s="5" t="inlineStr"/>
       <c r="O44" s="5" t="inlineStr"/>
       <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q44" s="5" t="inlineStr"/>
       <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S44" s="5" t="inlineStr"/>
       <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U44" s="5" t="inlineStr"/>
       <c r="V44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
@@ -7747,42 +6811,18 @@
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="5" t="inlineStr"/>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L45" s="5" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N45" s="5" t="inlineStr"/>
       <c r="O45" s="5" t="inlineStr"/>
       <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q45" s="5" t="inlineStr"/>
       <c r="R45" s="5" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S45" s="5" t="inlineStr"/>
       <c r="T45" s="5" t="inlineStr"/>
-      <c r="U45" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U45" s="5" t="inlineStr"/>
       <c r="V45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
@@ -7811,42 +6851,18 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N46" s="5" t="inlineStr"/>
       <c r="O46" s="5" t="inlineStr"/>
       <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q46" s="5" t="inlineStr"/>
       <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S46" s="5" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U46" s="5" t="inlineStr"/>
       <c r="V46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
@@ -7875,42 +6891,18 @@
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U47" s="5" t="inlineStr"/>
       <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
@@ -7935,42 +6927,18 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N48" s="5" t="inlineStr"/>
       <c r="O48" s="5" t="inlineStr"/>
       <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S48" s="5" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr"/>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U48" s="5" t="inlineStr"/>
       <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
@@ -7999,42 +6967,18 @@
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N49" s="5" t="inlineStr"/>
       <c r="O49" s="5" t="inlineStr"/>
       <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U49" s="5" t="inlineStr"/>
       <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
@@ -8063,42 +7007,18 @@
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N50" s="5" t="inlineStr"/>
       <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S50" s="5" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U50" s="5" t="inlineStr"/>
       <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
@@ -8123,42 +7043,18 @@
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N51" s="5" t="inlineStr"/>
       <c r="O51" s="5" t="inlineStr"/>
       <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S51" s="5" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U51" s="5" t="inlineStr"/>
       <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
@@ -8187,42 +7083,18 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N52" s="5" t="inlineStr"/>
       <c r="O52" s="5" t="inlineStr"/>
       <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S52" s="5" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U52" s="5" t="inlineStr"/>
       <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
@@ -8251,42 +7123,18 @@
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S53" s="5" t="inlineStr"/>
       <c r="T53" s="5" t="inlineStr"/>
-      <c r="U53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U53" s="5" t="inlineStr"/>
       <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
@@ -8315,42 +7163,18 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N54" s="5" t="inlineStr"/>
       <c r="O54" s="5" t="inlineStr"/>
       <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q54" s="5" t="inlineStr"/>
       <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S54" s="5" t="inlineStr"/>
       <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U54" s="5" t="inlineStr"/>
       <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
@@ -8379,42 +7203,18 @@
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
       <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q55" s="5" t="inlineStr"/>
       <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S55" s="5" t="inlineStr"/>
       <c r="T55" s="5" t="inlineStr"/>
-      <c r="U55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U55" s="5" t="inlineStr"/>
       <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
@@ -8443,42 +7243,18 @@
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N56" s="5" t="inlineStr"/>
       <c r="O56" s="5" t="inlineStr"/>
       <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q56" s="5" t="inlineStr"/>
       <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S56" s="5" t="inlineStr"/>
       <c r="T56" s="5" t="inlineStr"/>
-      <c r="U56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U56" s="5" t="inlineStr"/>
       <c r="V56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
@@ -8507,42 +7283,18 @@
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J57" s="5" t="inlineStr"/>
       <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L57" s="5" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N57" s="5" t="inlineStr"/>
       <c r="O57" s="5" t="inlineStr"/>
       <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q57" s="5" t="inlineStr"/>
       <c r="R57" s="5" t="inlineStr"/>
-      <c r="S57" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S57" s="5" t="inlineStr"/>
       <c r="T57" s="5" t="inlineStr"/>
-      <c r="U57" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U57" s="5" t="inlineStr"/>
       <c r="V57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
@@ -8571,42 +7323,18 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L58" s="5" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N58" s="5" t="inlineStr"/>
       <c r="O58" s="5" t="inlineStr"/>
       <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q58" s="5" t="inlineStr"/>
       <c r="R58" s="5" t="inlineStr"/>
-      <c r="S58" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S58" s="5" t="inlineStr"/>
       <c r="T58" s="5" t="inlineStr"/>
-      <c r="U58" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U58" s="5" t="inlineStr"/>
       <c r="V58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
@@ -8635,42 +7363,18 @@
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L59" s="5" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N59" s="5" t="inlineStr"/>
       <c r="O59" s="5" t="inlineStr"/>
       <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q59" s="5" t="inlineStr"/>
       <c r="R59" s="5" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S59" s="5" t="inlineStr"/>
       <c r="T59" s="5" t="inlineStr"/>
-      <c r="U59" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U59" s="5" t="inlineStr"/>
       <c r="V59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
@@ -8695,42 +7399,18 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr"/>
-      <c r="L60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L60" s="5" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N60" s="5" t="inlineStr"/>
       <c r="O60" s="5" t="inlineStr"/>
       <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q60" s="5" t="inlineStr"/>
       <c r="R60" s="5" t="inlineStr"/>
-      <c r="S60" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S60" s="5" t="inlineStr"/>
       <c r="T60" s="5" t="inlineStr"/>
-      <c r="U60" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U60" s="5" t="inlineStr"/>
       <c r="V60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
@@ -8755,42 +7435,18 @@
       <c r="G61" s="5" t="inlineStr"/>
       <c r="H61" s="5" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="5" t="inlineStr"/>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
-      <c r="N61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N61" s="5" t="inlineStr"/>
       <c r="O61" s="5" t="inlineStr"/>
       <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q61" s="5" t="inlineStr"/>
       <c r="R61" s="5" t="inlineStr"/>
-      <c r="S61" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S61" s="5" t="inlineStr"/>
       <c r="T61" s="5" t="inlineStr"/>
-      <c r="U61" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U61" s="5" t="inlineStr"/>
       <c r="V61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
@@ -8815,42 +7471,18 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="5" t="inlineStr"/>
-      <c r="N62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N62" s="5" t="inlineStr"/>
       <c r="O62" s="5" t="inlineStr"/>
       <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q62" s="5" t="inlineStr"/>
       <c r="R62" s="5" t="inlineStr"/>
-      <c r="S62" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S62" s="5" t="inlineStr"/>
       <c r="T62" s="5" t="inlineStr"/>
-      <c r="U62" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U62" s="5" t="inlineStr"/>
       <c r="V62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
@@ -8875,42 +7507,18 @@
       <c r="G63" s="5" t="inlineStr"/>
       <c r="H63" s="5" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="5" t="inlineStr"/>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="5" t="inlineStr"/>
-      <c r="N63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N63" s="5" t="inlineStr"/>
       <c r="O63" s="5" t="inlineStr"/>
       <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="inlineStr"/>
-      <c r="S63" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S63" s="5" t="inlineStr"/>
       <c r="T63" s="5" t="inlineStr"/>
-      <c r="U63" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U63" s="5" t="inlineStr"/>
       <c r="V63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
@@ -8935,42 +7543,18 @@
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr"/>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="5" t="inlineStr"/>
-      <c r="N64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N64" s="5" t="inlineStr"/>
       <c r="O64" s="5" t="inlineStr"/>
       <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q64" s="5" t="inlineStr"/>
       <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S64" s="5" t="inlineStr"/>
       <c r="T64" s="5" t="inlineStr"/>
-      <c r="U64" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U64" s="5" t="inlineStr"/>
       <c r="V64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
@@ -8995,42 +7579,18 @@
       <c r="G65" s="5" t="inlineStr"/>
       <c r="H65" s="5" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J65" s="5" t="inlineStr"/>
       <c r="K65" s="5" t="inlineStr"/>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="5" t="inlineStr"/>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N65" s="5" t="inlineStr"/>
       <c r="O65" s="5" t="inlineStr"/>
       <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q65" s="5" t="inlineStr"/>
       <c r="R65" s="5" t="inlineStr"/>
-      <c r="S65" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S65" s="5" t="inlineStr"/>
       <c r="T65" s="5" t="inlineStr"/>
-      <c r="U65" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U65" s="5" t="inlineStr"/>
       <c r="V65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
@@ -9055,42 +7615,18 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr"/>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
-      <c r="N66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N66" s="5" t="inlineStr"/>
       <c r="O66" s="5" t="inlineStr"/>
       <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q66" s="5" t="inlineStr"/>
       <c r="R66" s="5" t="inlineStr"/>
-      <c r="S66" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S66" s="5" t="inlineStr"/>
       <c r="T66" s="5" t="inlineStr"/>
-      <c r="U66" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U66" s="5" t="inlineStr"/>
       <c r="V66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
@@ -9119,42 +7655,18 @@
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N67" s="5" t="inlineStr"/>
       <c r="O67" s="5" t="inlineStr"/>
       <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q67" s="5" t="inlineStr"/>
       <c r="R67" s="5" t="inlineStr"/>
-      <c r="S67" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S67" s="5" t="inlineStr"/>
       <c r="T67" s="5" t="inlineStr"/>
-      <c r="U67" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U67" s="5" t="inlineStr"/>
       <c r="V67" s="5" t="inlineStr"/>
     </row>
   </sheetData>

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ELI Near Term</t>
+          <t>ELI Near Term (2026-28)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ELI Med Term</t>
+          <t>ELI Med Term (2030-35)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="n">
-        <v>0.283</v>
+        <v>0.2827</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0.547516873654646</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
         <v>0.265</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.3426</v>
+        <v>0.3429</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1088,10 +1088,10 @@
         <v>220</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.0243</v>
+        <v>0.0214</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0.390717855103594</v>
@@ -1152,9 +1152,21 @@
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Central North Victoria</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -1179,14 +1191,30 @@
       <c r="Q8" s="5" t="n">
         <v>0.9211</v>
       </c>
-      <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-      <c r="U8" s="6" t="inlineStr"/>
-      <c r="V8" s="6" t="inlineStr"/>
-      <c r="W8" s="6" t="inlineStr"/>
-      <c r="X8" s="6" t="inlineStr"/>
-      <c r="Y8" s="6" t="inlineStr"/>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W8" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X8" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y8" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1270,7 +1298,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1288,7 +1316,7 @@
         <v>0.1687</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.1716</v>
+        <v>0.1709</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -1365,9 +1393,17 @@
       <c r="L11" s="5" t="n">
         <v>0.1812</v>
       </c>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
+      <c r="M11" s="5" t="n">
+        <v>0.547516873654646</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.122422882740379</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P11" s="5" t="n">
         <v>0.9329</v>
       </c>
@@ -1416,7 +1452,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1434,7 +1470,7 @@
         <v>0.1136</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1491</v>
+        <v>0.1487</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -1558,7 +1594,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="n">
-        <v>0.4115</v>
+        <v>0.4116</v>
       </c>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
@@ -1611,7 +1647,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1629,7 +1665,7 @@
         <v>0.1415</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.3001</v>
+        <v>0.3003</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1755,7 +1791,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1850,7 +1886,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1943,7 +1979,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2020,7 +2056,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2038,7 +2074,7 @@
         <v>0.2487</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.241</v>
+        <v>0.2407</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -2099,9 +2135,21 @@
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2115,25 +2163,49 @@
         <v>0.0488</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
+        <v>0.0712</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0.333698960112703</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>0.0595847221163789</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P21" s="5" t="n">
         <v>0.9031</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0.898</v>
       </c>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr"/>
-      <c r="U21" s="6" t="inlineStr"/>
-      <c r="V21" s="6" t="inlineStr"/>
-      <c r="W21" s="6" t="inlineStr"/>
-      <c r="X21" s="6" t="inlineStr"/>
-      <c r="Y21" s="6" t="inlineStr"/>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W21" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X21" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2152,9 +2224,21 @@
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2205,9 +2289,21 @@
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2221,7 +2317,7 @@
         <v>0.2029</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.0827</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
@@ -2232,14 +2328,30 @@
       <c r="Q23" s="5" t="n">
         <v>0.9436</v>
       </c>
-      <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr"/>
-      <c r="U23" s="6" t="inlineStr"/>
-      <c r="V23" s="6" t="inlineStr"/>
-      <c r="W23" s="6" t="inlineStr"/>
-      <c r="X23" s="6" t="inlineStr"/>
-      <c r="Y23" s="6" t="inlineStr"/>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W23" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X23" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y23" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2258,9 +2370,21 @@
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2285,14 +2409,30 @@
       <c r="Q24" s="5" t="n">
         <v>0.9436</v>
       </c>
-      <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr"/>
-      <c r="U24" s="6" t="inlineStr"/>
-      <c r="V24" s="6" t="inlineStr"/>
-      <c r="W24" s="6" t="inlineStr"/>
-      <c r="X24" s="6" t="inlineStr"/>
-      <c r="Y24" s="6" t="inlineStr"/>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W24" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X24" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y24" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2311,9 +2451,21 @@
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2324,28 +2476,52 @@
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0281</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
+        <v>0.0114</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0.355476340126375</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>0.0145227624959478</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P25" s="5" t="n">
         <v>0.8907</v>
       </c>
       <c r="Q25" s="5" t="n">
         <v>0.8868</v>
       </c>
-      <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr"/>
-      <c r="U25" s="6" t="inlineStr"/>
-      <c r="V25" s="6" t="inlineStr"/>
-      <c r="W25" s="6" t="inlineStr"/>
-      <c r="X25" s="6" t="inlineStr"/>
-      <c r="Y25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W25" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X25" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y25" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2460,9 +2636,21 @@
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2476,7 +2664,7 @@
         <v>0.099</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.1302</v>
+        <v>0.1301</v>
       </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
@@ -2611,9 +2799,21 @@
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2624,10 +2824,10 @@
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="5" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0762</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.2036</v>
+        <v>0.2019</v>
       </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
@@ -2638,14 +2838,30 @@
       <c r="Q31" s="5" t="n">
         <v>0.8966</v>
       </c>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
-      <c r="U31" s="6" t="inlineStr"/>
-      <c r="V31" s="6" t="inlineStr"/>
-      <c r="W31" s="6" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr"/>
-      <c r="Y31" s="6" t="inlineStr"/>
+      <c r="R31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X31" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y31" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2713,9 +2929,21 @@
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2726,7 +2954,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="5" t="n">
-        <v>0.1331</v>
+        <v>0.1329</v>
       </c>
       <c r="L33" s="5" t="n">
         <v>0.2152</v>
@@ -2740,14 +2968,30 @@
       <c r="Q33" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr"/>
-      <c r="V33" s="6" t="inlineStr"/>
-      <c r="W33" s="6" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr"/>
-      <c r="Y33" s="6" t="inlineStr"/>
+      <c r="R33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X33" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y33" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2766,9 +3010,21 @@
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2782,7 +3038,7 @@
         <v>0.0488</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.0623</v>
+        <v>0.0616</v>
       </c>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
@@ -2793,14 +3049,30 @@
       <c r="Q34" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr"/>
-      <c r="U34" s="6" t="inlineStr"/>
-      <c r="V34" s="6" t="inlineStr"/>
-      <c r="W34" s="6" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
-      <c r="Y34" s="6" t="inlineStr"/>
+      <c r="R34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W34" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X34" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y34" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2819,9 +3091,21 @@
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2832,10 +3116,10 @@
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="5" t="n">
-        <v>0.0345</v>
+        <v>0.0344</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0341</v>
       </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
@@ -2846,14 +3130,30 @@
       <c r="Q35" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
-      <c r="V35" s="6" t="inlineStr"/>
-      <c r="W35" s="6" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr"/>
-      <c r="Y35" s="6" t="inlineStr"/>
+      <c r="R35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W35" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X35" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y35" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2872,9 +3172,21 @@
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -2886,25 +3198,49 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="n">
-        <v>0.3163</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+        <v>0.316</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0.309991353939951</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0.06472709871080649</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P36" s="5" t="n">
         <v>0.9569</v>
       </c>
       <c r="Q36" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr"/>
-      <c r="V36" s="6" t="inlineStr"/>
-      <c r="W36" s="6" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr"/>
-      <c r="Y36" s="6" t="inlineStr"/>
+      <c r="R36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W36" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X36" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y36" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3017,9 +3353,21 @@
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3031,7 +3379,7 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="n">
-        <v>0.3291</v>
+        <v>0.3294</v>
       </c>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3042,14 +3390,30 @@
       <c r="Q39" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr"/>
-      <c r="U39" s="6" t="inlineStr"/>
-      <c r="V39" s="6" t="inlineStr"/>
-      <c r="W39" s="6" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr"/>
-      <c r="Y39" s="6" t="inlineStr"/>
+      <c r="R39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X39" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y39" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3068,9 +3432,21 @@
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3082,7 +3458,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="n">
-        <v>0.3505</v>
+        <v>0.3508</v>
       </c>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3093,14 +3469,30 @@
       <c r="Q40" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
-      <c r="Y40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X40" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y40" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3119,9 +3511,21 @@
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3133,7 +3537,7 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="n">
-        <v>0.2154</v>
+        <v>0.2153</v>
       </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3144,14 +3548,30 @@
       <c r="Q41" s="5" t="n">
         <v>0.9815</v>
       </c>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
-      <c r="V41" s="6" t="inlineStr"/>
-      <c r="W41" s="6" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr"/>
-      <c r="Y41" s="6" t="inlineStr"/>
+      <c r="R41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X41" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y41" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3268,9 +3688,21 @@
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3284,7 +3716,7 @@
         <v>0.1828</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.2573</v>
+        <v>0.2574</v>
       </c>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3295,14 +3727,30 @@
       <c r="Q44" s="5" t="n">
         <v>0.9822</v>
       </c>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
-      <c r="V44" s="6" t="inlineStr"/>
-      <c r="W44" s="6" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr"/>
-      <c r="Y44" s="6" t="inlineStr"/>
+      <c r="R44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W44" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X44" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y44" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3370,9 +3818,21 @@
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3386,7 +3846,7 @@
         <v>0.1789</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.2955</v>
+        <v>0.2954</v>
       </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3397,14 +3857,30 @@
       <c r="Q46" s="5" t="n">
         <v>0.8954</v>
       </c>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr"/>
-      <c r="Y46" s="6" t="inlineStr"/>
+      <c r="R46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W46" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X46" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y46" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3423,9 +3899,21 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3439,7 +3927,7 @@
         <v>0.1393</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.2357</v>
+        <v>0.2358</v>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3450,14 +3938,30 @@
       <c r="Q47" s="5" t="n">
         <v>0.9824000000000001</v>
       </c>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
-      <c r="Y47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W47" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X47" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y47" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3525,9 +4029,21 @@
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3541,25 +4057,49 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.08890000000000001</v>
-      </c>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
+        <v>0.0886</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0.309110166062179</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0.0785492513422225</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P49" s="5" t="n">
         <v>0.9569</v>
       </c>
       <c r="Q49" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
-      <c r="Y49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W49" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X49" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y49" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3578,9 +4118,21 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3594,25 +4146,49 @@
         <v>0.106</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
+        <v>0.023</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0.207260983484178</v>
+      </c>
+      <c r="N50" s="5" t="n">
+        <v>0.0933762231820911</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P50" s="5" t="n">
         <v>0.9525</v>
       </c>
       <c r="Q50" s="5" t="n">
         <v>0.9507</v>
       </c>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
-      <c r="Y50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W50" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X50" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y50" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3680,9 +4256,21 @@
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3693,10 +4281,10 @@
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="5" t="n">
-        <v>0.0528</v>
+        <v>0.0523</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0323</v>
       </c>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="inlineStr"/>
@@ -3707,14 +4295,30 @@
       <c r="Q52" s="5" t="n">
         <v>0.989</v>
       </c>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
-      <c r="Y52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W52" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X52" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y52" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3733,9 +4337,21 @@
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3749,7 +4365,7 @@
         <v>0.2792</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.1579</v>
+        <v>0.1581</v>
       </c>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="inlineStr"/>
@@ -3760,14 +4376,30 @@
       <c r="Q53" s="5" t="n">
         <v>0.9556</v>
       </c>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr"/>
-      <c r="V53" s="6" t="inlineStr"/>
-      <c r="W53" s="6" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr"/>
-      <c r="Y53" s="6" t="inlineStr"/>
+      <c r="R53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W53" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X53" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y53" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3786,9 +4418,21 @@
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3802,7 +4446,7 @@
         <v>0.2955</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.4223</v>
+        <v>0.4217</v>
       </c>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="inlineStr"/>
@@ -3813,14 +4457,30 @@
       <c r="Q54" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
-      <c r="Y54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W54" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X54" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y54" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3839,9 +4499,21 @@
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3855,7 +4527,7 @@
         <v>0.2502</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.3057</v>
+        <v>0.3047</v>
       </c>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
@@ -3866,14 +4538,30 @@
       <c r="Q55" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr"/>
-      <c r="V55" s="6" t="inlineStr"/>
-      <c r="W55" s="6" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr"/>
-      <c r="Y55" s="6" t="inlineStr"/>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W55" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X55" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y55" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3892,9 +4580,21 @@
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3908,7 +4608,7 @@
         <v>0.0793</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.1657</v>
+        <v>0.1656</v>
       </c>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="inlineStr"/>
@@ -3919,14 +4619,30 @@
       <c r="Q56" s="5" t="n">
         <v>0.9949</v>
       </c>
-      <c r="R56" s="6" t="inlineStr"/>
-      <c r="S56" s="6" t="inlineStr"/>
-      <c r="T56" s="6" t="inlineStr"/>
-      <c r="U56" s="6" t="inlineStr"/>
-      <c r="V56" s="6" t="inlineStr"/>
-      <c r="W56" s="6" t="inlineStr"/>
-      <c r="X56" s="6" t="inlineStr"/>
-      <c r="Y56" s="6" t="inlineStr"/>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W56" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X56" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y56" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3945,9 +4661,21 @@
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -3972,14 +4700,30 @@
       <c r="Q57" s="5" t="n">
         <v>0.983</v>
       </c>
-      <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="6" t="inlineStr"/>
-      <c r="T57" s="6" t="inlineStr"/>
-      <c r="U57" s="6" t="inlineStr"/>
-      <c r="V57" s="6" t="inlineStr"/>
-      <c r="W57" s="6" t="inlineStr"/>
-      <c r="X57" s="6" t="inlineStr"/>
-      <c r="Y57" s="6" t="inlineStr"/>
+      <c r="R57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W57" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X57" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y57" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3998,9 +4742,21 @@
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -4011,10 +4767,10 @@
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="5" t="n">
-        <v>0.2439</v>
+        <v>0.2438</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.3905</v>
+        <v>0.3904</v>
       </c>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4025,14 +4781,30 @@
       <c r="Q58" s="5" t="n">
         <v>0.9499</v>
       </c>
-      <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="6" t="inlineStr"/>
-      <c r="T58" s="6" t="inlineStr"/>
-      <c r="U58" s="6" t="inlineStr"/>
-      <c r="V58" s="6" t="inlineStr"/>
-      <c r="W58" s="6" t="inlineStr"/>
-      <c r="X58" s="6" t="inlineStr"/>
-      <c r="Y58" s="6" t="inlineStr"/>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W58" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X58" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y58" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4051,9 +4823,21 @@
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>South West Victoria</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -4064,10 +4848,10 @@
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0203</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.006</v>
       </c>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4078,14 +4862,30 @@
       <c r="Q59" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="6" t="inlineStr"/>
-      <c r="T59" s="6" t="inlineStr"/>
-      <c r="U59" s="6" t="inlineStr"/>
-      <c r="V59" s="6" t="inlineStr"/>
-      <c r="W59" s="6" t="inlineStr"/>
-      <c r="X59" s="6" t="inlineStr"/>
-      <c r="Y59" s="6" t="inlineStr"/>
+      <c r="R59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W59" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X59" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y59" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4447,9 +5247,21 @@
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Western Victoria</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>VIC</t>
@@ -4463,7 +5275,7 @@
         <v>0.1684</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.2925</v>
+        <v>0.2921</v>
       </c>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="inlineStr"/>
@@ -4474,14 +5286,30 @@
       <c r="Q67" s="5" t="n">
         <v>0.9547</v>
       </c>
-      <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="inlineStr"/>
-      <c r="T67" s="6" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr"/>
-      <c r="V67" s="6" t="inlineStr"/>
-      <c r="W67" s="6" t="inlineStr"/>
-      <c r="X67" s="6" t="inlineStr"/>
-      <c r="Y67" s="6" t="inlineStr"/>
+      <c r="R67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W67" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X67" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Y67" s="6" t="n">
+        <v>0.04</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4772,7 +5600,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="5" t="n">
-        <v>0.283</v>
+        <v>0.2827</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.547516873654646</v>
@@ -4940,7 +5768,7 @@
         <v>0.265</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3426</v>
+        <v>0.3429</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -5021,10 +5849,10 @@
         <v>0.9294</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.0243</v>
+        <v>0.0214</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.390717855103594</v>
@@ -5112,20 +5940,60 @@
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -5184,7 +6052,7 @@
         <v>0.1687</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1716</v>
+        <v>0.1709</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -5268,8 +6136,12 @@
       <c r="F11" s="5" t="n">
         <v>0.1812</v>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="n">
+        <v>0.547516873654646</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.122422882740379</v>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="5" t="inlineStr"/>
@@ -5306,7 +6178,7 @@
         <v>0.1136</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1491</v>
+        <v>0.1487</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -5424,7 +6296,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="n">
-        <v>0.4115</v>
+        <v>0.4116</v>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
@@ -5464,7 +6336,7 @@
         <v>0.1415</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3001</v>
+        <v>0.3003</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -5757,42 +6629,18 @@
         <v>0.08205629867681941</v>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L19" s="5" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
       <c r="R19" s="5" t="inlineStr"/>
-      <c r="S19" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S19" s="5" t="inlineStr"/>
       <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
@@ -5816,7 +6664,7 @@
         <v>0.2487</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.241</v>
+        <v>0.2407</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -5900,24 +6748,68 @@
         <v>0.0488</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="5" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="5" t="inlineStr"/>
-      <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="5" t="inlineStr"/>
-      <c r="Q21" s="5" t="inlineStr"/>
-      <c r="R21" s="5" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr"/>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr"/>
-      <c r="V21" s="5" t="inlineStr"/>
+        <v>0.0712</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.333698960112703</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.0595847221163789</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -5980,24 +6872,64 @@
         <v>0.2029</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0827</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="5" t="inlineStr"/>
-      <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="5" t="inlineStr"/>
-      <c r="Q23" s="5" t="inlineStr"/>
-      <c r="R23" s="5" t="inlineStr"/>
-      <c r="S23" s="5" t="inlineStr"/>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr"/>
-      <c r="V23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R23" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -6024,20 +6956,60 @@
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr"/>
-      <c r="V24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -6057,27 +7029,71 @@
         <v>0.8868</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0281</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr"/>
-      <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr"/>
-      <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr"/>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr"/>
-      <c r="V25" s="5" t="inlineStr"/>
+        <v>0.0114</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.355476340126375</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.0145227624959478</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6170,7 +7186,7 @@
         <v>0.099</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.1302</v>
+        <v>0.1301</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -6279,27 +7295,67 @@
         <v>0.8966</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0762</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.2036</v>
+        <v>0.2019</v>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr"/>
-      <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr"/>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr"/>
-      <c r="V31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S31" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6355,27 +7411,67 @@
         <v>0.9827</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.1331</v>
+        <v>0.1329</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>0.2152</v>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="5" t="inlineStr"/>
-      <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="5" t="inlineStr"/>
-      <c r="Q33" s="5" t="inlineStr"/>
-      <c r="R33" s="5" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr"/>
-      <c r="T33" s="5" t="inlineStr"/>
-      <c r="U33" s="5" t="inlineStr"/>
-      <c r="V33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U33" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6398,24 +7494,64 @@
         <v>0.0488</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0623</v>
+        <v>0.0616</v>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="5" t="inlineStr"/>
-      <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="5" t="inlineStr"/>
-      <c r="Q34" s="5" t="inlineStr"/>
-      <c r="R34" s="5" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr"/>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q34" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U34" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -6435,27 +7571,67 @@
         <v>0.9827</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.0345</v>
+        <v>0.0344</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0341</v>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr"/>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="5" t="inlineStr"/>
-      <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="5" t="inlineStr"/>
-      <c r="Q35" s="5" t="inlineStr"/>
-      <c r="R35" s="5" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr"/>
-      <c r="T35" s="5" t="inlineStr"/>
-      <c r="U35" s="5" t="inlineStr"/>
-      <c r="V35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q35" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R35" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U35" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -6476,24 +7652,68 @@
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="n">
-        <v>0.3163</v>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="inlineStr"/>
-      <c r="U36" s="5" t="inlineStr"/>
-      <c r="V36" s="5" t="inlineStr"/>
+        <v>0.316</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.309991353939951</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.06472709871080649</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q36" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -6582,24 +7802,64 @@
       </c>
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="n">
-        <v>0.3291</v>
+        <v>0.3294</v>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="5" t="inlineStr"/>
-      <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="5" t="inlineStr"/>
-      <c r="Q39" s="5" t="inlineStr"/>
-      <c r="R39" s="5" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr"/>
-      <c r="T39" s="5" t="inlineStr"/>
-      <c r="U39" s="5" t="inlineStr"/>
-      <c r="V39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q39" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -6620,24 +7880,64 @@
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="n">
-        <v>0.3505</v>
+        <v>0.3508</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -6658,24 +7958,64 @@
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="n">
-        <v>0.2154</v>
+        <v>0.2153</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
-      <c r="K41" s="5" t="inlineStr"/>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="5" t="inlineStr"/>
-      <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-      <c r="R41" s="5" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr"/>
-      <c r="T41" s="5" t="inlineStr"/>
-      <c r="U41" s="5" t="inlineStr"/>
-      <c r="V41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q41" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S41" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U41" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V41" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -6770,24 +8110,64 @@
         <v>0.1828</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.2573</v>
+        <v>0.2574</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="5" t="inlineStr"/>
-      <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="5" t="inlineStr"/>
-      <c r="Q44" s="5" t="inlineStr"/>
-      <c r="R44" s="5" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr"/>
-      <c r="T44" s="5" t="inlineStr"/>
-      <c r="U44" s="5" t="inlineStr"/>
-      <c r="V44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U44" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V44" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -6846,24 +8226,64 @@
         <v>0.1789</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2955</v>
+        <v>0.2954</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="5" t="inlineStr"/>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
-      <c r="R46" s="5" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr"/>
-      <c r="T46" s="5" t="inlineStr"/>
-      <c r="U46" s="5" t="inlineStr"/>
-      <c r="V46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R46" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S46" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U46" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V46" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -6886,24 +8306,64 @@
         <v>0.1393</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.2357</v>
+        <v>0.2358</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -6962,24 +8422,68 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.08890000000000001</v>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr"/>
+        <v>0.0886</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.309110166062179</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.0785492513422225</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -7002,24 +8506,68 @@
         <v>0.106</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0231</v>
-      </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr"/>
+        <v>0.023</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.207260983484178</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.0933762231820911</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -7075,27 +8623,67 @@
         <v>0.989</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0528</v>
+        <v>0.0523</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0323</v>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -7118,24 +8706,64 @@
         <v>0.2792</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.1579</v>
+        <v>0.1581</v>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr"/>
-      <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-      <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr"/>
-      <c r="T53" s="5" t="inlineStr"/>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T53" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U53" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V53" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -7158,24 +8786,64 @@
         <v>0.2955</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.4223</v>
+        <v>0.4217</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -7198,24 +8866,64 @@
         <v>0.2502</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.3057</v>
+        <v>0.3047</v>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-      <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr"/>
-      <c r="T55" s="5" t="inlineStr"/>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q55" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S55" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T55" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U55" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V55" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -7238,24 +8946,64 @@
         <v>0.0793</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.1657</v>
+        <v>0.1656</v>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="inlineStr"/>
-      <c r="O56" s="5" t="inlineStr"/>
-      <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr"/>
-      <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr"/>
-      <c r="T56" s="5" t="inlineStr"/>
-      <c r="U56" s="5" t="inlineStr"/>
-      <c r="V56" s="5" t="inlineStr"/>
+      <c r="I56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q56" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R56" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U56" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V56" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -7282,20 +9030,60 @@
       </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="5" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="5" t="inlineStr"/>
-      <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr"/>
-      <c r="R57" s="5" t="inlineStr"/>
-      <c r="S57" s="5" t="inlineStr"/>
-      <c r="T57" s="5" t="inlineStr"/>
-      <c r="U57" s="5" t="inlineStr"/>
-      <c r="V57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q57" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R57" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S57" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T57" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U57" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V57" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -7315,27 +9103,67 @@
         <v>0.9499</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.2439</v>
+        <v>0.2438</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.3905</v>
+        <v>0.3904</v>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr"/>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="5" t="inlineStr"/>
-      <c r="O58" s="5" t="inlineStr"/>
-      <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr"/>
-      <c r="R58" s="5" t="inlineStr"/>
-      <c r="S58" s="5" t="inlineStr"/>
-      <c r="T58" s="5" t="inlineStr"/>
-      <c r="U58" s="5" t="inlineStr"/>
-      <c r="V58" s="5" t="inlineStr"/>
+      <c r="I58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q58" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R58" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S58" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U58" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V58" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -7355,27 +9183,67 @@
         <v>0.9827</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.0222</v>
+        <v>0.0203</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.0083</v>
+        <v>0.006</v>
       </c>
       <c r="G59" s="5" t="inlineStr"/>
       <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr"/>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="5" t="inlineStr"/>
-      <c r="O59" s="5" t="inlineStr"/>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr"/>
-      <c r="R59" s="5" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr"/>
-      <c r="T59" s="5" t="inlineStr"/>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" s="5" t="inlineStr"/>
+      <c r="I59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R59" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S59" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U59" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V59" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -7650,24 +9518,64 @@
         <v>0.1684</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.2925</v>
+        <v>0.2921</v>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr"/>
-      <c r="L67" s="5" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="5" t="inlineStr"/>
-      <c r="O67" s="5" t="inlineStr"/>
-      <c r="P67" s="5" t="inlineStr"/>
-      <c r="Q67" s="5" t="inlineStr"/>
-      <c r="R67" s="5" t="inlineStr"/>
-      <c r="S67" s="5" t="inlineStr"/>
-      <c r="T67" s="5" t="inlineStr"/>
-      <c r="U67" s="5" t="inlineStr"/>
-      <c r="V67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T67" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="U67" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V67" s="5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C67">

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P2" s="5" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P4" s="5" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P5" s="5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P6" s="5" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P7" s="5" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P10" s="5" t="n">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P12" s="5" t="n">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P15" s="5" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P17" s="5" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P18" s="5" t="n">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P19" s="5" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P20" s="5" t="n">

--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:AG67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,14 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,6 +620,46 @@
           <t>Offl Avg</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ match</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2029-30</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2039-40</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2049-50</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2029-30</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2039-40</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2049-50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -707,6 +755,18 @@
       <c r="Y2" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB2" s="6" t="inlineStr"/>
+      <c r="AC2" s="6" t="inlineStr"/>
+      <c r="AD2" s="6" t="inlineStr"/>
+      <c r="AE2" s="6" t="inlineStr"/>
+      <c r="AF2" s="6" t="inlineStr"/>
+      <c r="AG2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -756,6 +816,14 @@
       <c r="W3" s="6" t="inlineStr"/>
       <c r="X3" s="6" t="inlineStr"/>
       <c r="Y3" s="6" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="6" t="inlineStr"/>
+      <c r="AC3" s="6" t="inlineStr"/>
+      <c r="AD3" s="6" t="inlineStr"/>
+      <c r="AE3" s="6" t="inlineStr"/>
+      <c r="AF3" s="6" t="inlineStr"/>
+      <c r="AG3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -849,6 +917,18 @@
       <c r="Y4" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB4" s="6" t="inlineStr"/>
+      <c r="AC4" s="6" t="inlineStr"/>
+      <c r="AD4" s="6" t="inlineStr"/>
+      <c r="AE4" s="6" t="inlineStr"/>
+      <c r="AF4" s="6" t="inlineStr"/>
+      <c r="AG4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -944,6 +1024,18 @@
       <c r="Y5" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="inlineStr"/>
+      <c r="AC5" s="6" t="inlineStr"/>
+      <c r="AD5" s="6" t="inlineStr"/>
+      <c r="AE5" s="6" t="inlineStr"/>
+      <c r="AF5" s="6" t="inlineStr"/>
+      <c r="AG5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1039,6 +1131,34 @@
       <c r="Y6" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>Central North</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB6" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE6" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF6" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG6" s="6" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1133,6 +1253,34 @@
       </c>
       <c r="Y7" s="6" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>Central North</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB7" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE7" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF7" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG7" s="6" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="8">
@@ -1214,6 +1362,34 @@
       </c>
       <c r="Y8" s="6" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>Central North</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE8" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF8" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG8" s="6" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="9">
@@ -1264,6 +1440,14 @@
       <c r="W9" s="6" t="inlineStr"/>
       <c r="X9" s="6" t="inlineStr"/>
       <c r="Y9" s="6" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="6" t="inlineStr"/>
+      <c r="AC9" s="6" t="inlineStr"/>
+      <c r="AD9" s="6" t="inlineStr"/>
+      <c r="AE9" s="6" t="inlineStr"/>
+      <c r="AF9" s="6" t="inlineStr"/>
+      <c r="AG9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1359,6 +1543,18 @@
       <c r="Y10" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="6" t="inlineStr"/>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="6" t="inlineStr"/>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1418,6 +1614,14 @@
       <c r="W11" s="6" t="inlineStr"/>
       <c r="X11" s="6" t="inlineStr"/>
       <c r="Y11" s="6" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="6" t="inlineStr"/>
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="6" t="inlineStr"/>
+      <c r="AF11" s="6" t="inlineStr"/>
+      <c r="AG11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1513,6 +1717,18 @@
       <c r="Y12" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="inlineStr"/>
+      <c r="AC12" s="6" t="inlineStr"/>
+      <c r="AD12" s="6" t="inlineStr"/>
+      <c r="AE12" s="6" t="inlineStr"/>
+      <c r="AF12" s="6" t="inlineStr"/>
+      <c r="AG12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1562,6 +1778,14 @@
       <c r="W13" s="6" t="inlineStr"/>
       <c r="X13" s="6" t="inlineStr"/>
       <c r="Y13" s="6" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="6" t="inlineStr"/>
+      <c r="AC13" s="6" t="inlineStr"/>
+      <c r="AD13" s="6" t="inlineStr"/>
+      <c r="AE13" s="6" t="inlineStr"/>
+      <c r="AF13" s="6" t="inlineStr"/>
+      <c r="AG13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1613,6 +1837,14 @@
       <c r="W14" s="6" t="inlineStr"/>
       <c r="X14" s="6" t="inlineStr"/>
       <c r="Y14" s="6" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="6" t="inlineStr"/>
+      <c r="AD14" s="6" t="inlineStr"/>
+      <c r="AE14" s="6" t="inlineStr"/>
+      <c r="AF14" s="6" t="inlineStr"/>
+      <c r="AG14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1707,6 +1939,34 @@
       </c>
       <c r="Y15" s="6" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>Central North</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE15" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF15" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG15" s="6" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="16">
@@ -1757,6 +2017,14 @@
       <c r="W16" s="6" t="inlineStr"/>
       <c r="X16" s="6" t="inlineStr"/>
       <c r="Y16" s="6" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="6" t="inlineStr"/>
+      <c r="AD16" s="6" t="inlineStr"/>
+      <c r="AE16" s="6" t="inlineStr"/>
+      <c r="AF16" s="6" t="inlineStr"/>
+      <c r="AG16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1852,6 +2120,18 @@
       <c r="Y17" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="inlineStr"/>
+      <c r="AC17" s="6" t="inlineStr"/>
+      <c r="AD17" s="6" t="inlineStr"/>
+      <c r="AE17" s="6" t="inlineStr"/>
+      <c r="AF17" s="6" t="inlineStr"/>
+      <c r="AG17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1944,6 +2224,34 @@
       </c>
       <c r="Y18" s="6" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>Central North</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB18" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE18" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF18" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG18" s="6" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="19">
@@ -2022,6 +2330,14 @@
       <c r="W19" s="6" t="inlineStr"/>
       <c r="X19" s="6" t="inlineStr"/>
       <c r="Y19" s="6" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="6" t="inlineStr"/>
+      <c r="AD19" s="6" t="inlineStr"/>
+      <c r="AE19" s="6" t="inlineStr"/>
+      <c r="AF19" s="6" t="inlineStr"/>
+      <c r="AG19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2117,6 +2433,18 @@
       <c r="Y20" s="6" t="n">
         <v>0.12</v>
       </c>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB20" s="6" t="inlineStr"/>
+      <c r="AC20" s="6" t="inlineStr"/>
+      <c r="AD20" s="6" t="inlineStr"/>
+      <c r="AE20" s="6" t="inlineStr"/>
+      <c r="AF20" s="6" t="inlineStr"/>
+      <c r="AG20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2206,6 +2534,18 @@
       <c r="Y21" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB21" s="6" t="inlineStr"/>
+      <c r="AC21" s="6" t="inlineStr"/>
+      <c r="AD21" s="6" t="inlineStr"/>
+      <c r="AE21" s="6" t="inlineStr"/>
+      <c r="AF21" s="6" t="inlineStr"/>
+      <c r="AG21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2271,6 +2611,14 @@
       <c r="W22" s="6" t="inlineStr"/>
       <c r="X22" s="6" t="inlineStr"/>
       <c r="Y22" s="6" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="6" t="inlineStr"/>
+      <c r="AC22" s="6" t="inlineStr"/>
+      <c r="AD22" s="6" t="inlineStr"/>
+      <c r="AE22" s="6" t="inlineStr"/>
+      <c r="AF22" s="6" t="inlineStr"/>
+      <c r="AG22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2352,6 +2700,34 @@
       <c r="Y23" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF23" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG23" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2433,6 +2809,34 @@
       <c r="Y24" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF24" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG24" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2522,6 +2926,18 @@
       <c r="Y25" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB25" s="6" t="inlineStr"/>
+      <c r="AC25" s="6" t="inlineStr"/>
+      <c r="AD25" s="6" t="inlineStr"/>
+      <c r="AE25" s="6" t="inlineStr"/>
+      <c r="AF25" s="6" t="inlineStr"/>
+      <c r="AG25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2571,6 +2987,14 @@
       <c r="W26" s="6" t="inlineStr"/>
       <c r="X26" s="6" t="inlineStr"/>
       <c r="Y26" s="6" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="6" t="inlineStr"/>
+      <c r="AC26" s="6" t="inlineStr"/>
+      <c r="AD26" s="6" t="inlineStr"/>
+      <c r="AE26" s="6" t="inlineStr"/>
+      <c r="AF26" s="6" t="inlineStr"/>
+      <c r="AG26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2618,6 +3042,14 @@
       <c r="W27" s="6" t="inlineStr"/>
       <c r="X27" s="6" t="inlineStr"/>
       <c r="Y27" s="6" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="6" t="inlineStr"/>
+      <c r="AC27" s="6" t="inlineStr"/>
+      <c r="AD27" s="6" t="inlineStr"/>
+      <c r="AE27" s="6" t="inlineStr"/>
+      <c r="AF27" s="6" t="inlineStr"/>
+      <c r="AG27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2683,6 +3115,14 @@
       <c r="W28" s="6" t="inlineStr"/>
       <c r="X28" s="6" t="inlineStr"/>
       <c r="Y28" s="6" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="6" t="inlineStr"/>
+      <c r="AC28" s="6" t="inlineStr"/>
+      <c r="AD28" s="6" t="inlineStr"/>
+      <c r="AE28" s="6" t="inlineStr"/>
+      <c r="AF28" s="6" t="inlineStr"/>
+      <c r="AG28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2732,6 +3172,14 @@
       <c r="W29" s="6" t="inlineStr"/>
       <c r="X29" s="6" t="inlineStr"/>
       <c r="Y29" s="6" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="6" t="inlineStr"/>
+      <c r="AC29" s="6" t="inlineStr"/>
+      <c r="AD29" s="6" t="inlineStr"/>
+      <c r="AE29" s="6" t="inlineStr"/>
+      <c r="AF29" s="6" t="inlineStr"/>
+      <c r="AG29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2781,6 +3229,14 @@
       <c r="W30" s="6" t="inlineStr"/>
       <c r="X30" s="6" t="inlineStr"/>
       <c r="Y30" s="6" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="6" t="inlineStr"/>
+      <c r="AC30" s="6" t="inlineStr"/>
+      <c r="AD30" s="6" t="inlineStr"/>
+      <c r="AE30" s="6" t="inlineStr"/>
+      <c r="AF30" s="6" t="inlineStr"/>
+      <c r="AG30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2862,6 +3318,18 @@
       <c r="Y31" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB31" s="6" t="inlineStr"/>
+      <c r="AC31" s="6" t="inlineStr"/>
+      <c r="AD31" s="6" t="inlineStr"/>
+      <c r="AE31" s="6" t="inlineStr"/>
+      <c r="AF31" s="6" t="inlineStr"/>
+      <c r="AG31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2911,6 +3379,14 @@
       <c r="W32" s="6" t="inlineStr"/>
       <c r="X32" s="6" t="inlineStr"/>
       <c r="Y32" s="6" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="6" t="inlineStr"/>
+      <c r="AC32" s="6" t="inlineStr"/>
+      <c r="AD32" s="6" t="inlineStr"/>
+      <c r="AE32" s="6" t="inlineStr"/>
+      <c r="AF32" s="6" t="inlineStr"/>
+      <c r="AG32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2992,6 +3468,34 @@
       <c r="Y33" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF33" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG33" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3073,6 +3577,34 @@
       <c r="Y34" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF34" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG34" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3154,6 +3686,34 @@
       <c r="Y35" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF35" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG35" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3241,6 +3801,18 @@
       <c r="Y36" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB36" s="6" t="inlineStr"/>
+      <c r="AC36" s="6" t="inlineStr"/>
+      <c r="AD36" s="6" t="inlineStr"/>
+      <c r="AE36" s="6" t="inlineStr"/>
+      <c r="AF36" s="6" t="inlineStr"/>
+      <c r="AG36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3286,6 +3858,14 @@
       <c r="W37" s="6" t="inlineStr"/>
       <c r="X37" s="6" t="inlineStr"/>
       <c r="Y37" s="6" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="6" t="inlineStr"/>
+      <c r="AC37" s="6" t="inlineStr"/>
+      <c r="AD37" s="6" t="inlineStr"/>
+      <c r="AE37" s="6" t="inlineStr"/>
+      <c r="AF37" s="6" t="inlineStr"/>
+      <c r="AG37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3335,6 +3915,14 @@
       <c r="W38" s="6" t="inlineStr"/>
       <c r="X38" s="6" t="inlineStr"/>
       <c r="Y38" s="6" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="6" t="inlineStr"/>
+      <c r="AC38" s="6" t="inlineStr"/>
+      <c r="AD38" s="6" t="inlineStr"/>
+      <c r="AE38" s="6" t="inlineStr"/>
+      <c r="AF38" s="6" t="inlineStr"/>
+      <c r="AG38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3414,6 +4002,34 @@
       <c r="Y39" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF39" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG39" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3493,6 +4109,34 @@
       <c r="Y40" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF40" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG40" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3571,6 +4215,34 @@
       </c>
       <c r="Y41" s="6" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF41" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG41" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="42">
@@ -3621,6 +4293,14 @@
       <c r="W42" s="6" t="inlineStr"/>
       <c r="X42" s="6" t="inlineStr"/>
       <c r="Y42" s="6" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="6" t="inlineStr"/>
+      <c r="AC42" s="6" t="inlineStr"/>
+      <c r="AD42" s="6" t="inlineStr"/>
+      <c r="AE42" s="6" t="inlineStr"/>
+      <c r="AF42" s="6" t="inlineStr"/>
+      <c r="AG42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3670,6 +4350,14 @@
       <c r="W43" s="6" t="inlineStr"/>
       <c r="X43" s="6" t="inlineStr"/>
       <c r="Y43" s="6" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="6" t="inlineStr"/>
+      <c r="AC43" s="6" t="inlineStr"/>
+      <c r="AD43" s="6" t="inlineStr"/>
+      <c r="AE43" s="6" t="inlineStr"/>
+      <c r="AF43" s="6" t="inlineStr"/>
+      <c r="AG43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3750,6 +4438,34 @@
       </c>
       <c r="Y44" s="6" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF44" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG44" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="45">
@@ -3800,6 +4516,14 @@
       <c r="W45" s="6" t="inlineStr"/>
       <c r="X45" s="6" t="inlineStr"/>
       <c r="Y45" s="6" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="6" t="inlineStr"/>
+      <c r="AC45" s="6" t="inlineStr"/>
+      <c r="AD45" s="6" t="inlineStr"/>
+      <c r="AE45" s="6" t="inlineStr"/>
+      <c r="AF45" s="6" t="inlineStr"/>
+      <c r="AG45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3881,6 +4605,18 @@
       <c r="Y46" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB46" s="6" t="inlineStr"/>
+      <c r="AC46" s="6" t="inlineStr"/>
+      <c r="AD46" s="6" t="inlineStr"/>
+      <c r="AE46" s="6" t="inlineStr"/>
+      <c r="AF46" s="6" t="inlineStr"/>
+      <c r="AG46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3961,6 +4697,34 @@
       </c>
       <c r="Y47" s="6" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF47" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG47" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="48">
@@ -4011,6 +4775,14 @@
       <c r="W48" s="6" t="inlineStr"/>
       <c r="X48" s="6" t="inlineStr"/>
       <c r="Y48" s="6" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="6" t="inlineStr"/>
+      <c r="AC48" s="6" t="inlineStr"/>
+      <c r="AD48" s="6" t="inlineStr"/>
+      <c r="AE48" s="6" t="inlineStr"/>
+      <c r="AF48" s="6" t="inlineStr"/>
+      <c r="AG48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4100,6 +4872,18 @@
       <c r="Y49" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB49" s="6" t="inlineStr"/>
+      <c r="AC49" s="6" t="inlineStr"/>
+      <c r="AD49" s="6" t="inlineStr"/>
+      <c r="AE49" s="6" t="inlineStr"/>
+      <c r="AF49" s="6" t="inlineStr"/>
+      <c r="AG49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4188,6 +4972,34 @@
       </c>
       <c r="Y50" s="6" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF50" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG50" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="51">
@@ -4238,6 +5050,14 @@
       <c r="W51" s="6" t="inlineStr"/>
       <c r="X51" s="6" t="inlineStr"/>
       <c r="Y51" s="6" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="6" t="inlineStr"/>
+      <c r="AC51" s="6" t="inlineStr"/>
+      <c r="AD51" s="6" t="inlineStr"/>
+      <c r="AE51" s="6" t="inlineStr"/>
+      <c r="AF51" s="6" t="inlineStr"/>
+      <c r="AG51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4319,6 +5139,34 @@
       <c r="Y52" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF52" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG52" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4400,6 +5248,18 @@
       <c r="Y53" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB53" s="6" t="inlineStr"/>
+      <c r="AC53" s="6" t="inlineStr"/>
+      <c r="AD53" s="6" t="inlineStr"/>
+      <c r="AE53" s="6" t="inlineStr"/>
+      <c r="AF53" s="6" t="inlineStr"/>
+      <c r="AG53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4481,6 +5341,18 @@
       <c r="Y54" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB54" s="6" t="inlineStr"/>
+      <c r="AC54" s="6" t="inlineStr"/>
+      <c r="AD54" s="6" t="inlineStr"/>
+      <c r="AE54" s="6" t="inlineStr"/>
+      <c r="AF54" s="6" t="inlineStr"/>
+      <c r="AG54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4562,6 +5434,18 @@
       <c r="Y55" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB55" s="6" t="inlineStr"/>
+      <c r="AC55" s="6" t="inlineStr"/>
+      <c r="AD55" s="6" t="inlineStr"/>
+      <c r="AE55" s="6" t="inlineStr"/>
+      <c r="AF55" s="6" t="inlineStr"/>
+      <c r="AG55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4643,6 +5527,34 @@
       <c r="Y56" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF56" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG56" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4724,6 +5636,34 @@
       <c r="Y57" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF57" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG57" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4805,6 +5745,34 @@
       <c r="Y58" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF58" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG58" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4885,6 +5853,34 @@
       </c>
       <c r="Y59" s="6" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>South West</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AF59" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG59" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="60">
@@ -4935,6 +5931,14 @@
       <c r="W60" s="6" t="inlineStr"/>
       <c r="X60" s="6" t="inlineStr"/>
       <c r="Y60" s="6" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="6" t="inlineStr"/>
+      <c r="AC60" s="6" t="inlineStr"/>
+      <c r="AD60" s="6" t="inlineStr"/>
+      <c r="AE60" s="6" t="inlineStr"/>
+      <c r="AF60" s="6" t="inlineStr"/>
+      <c r="AG60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4984,6 +5988,14 @@
       <c r="W61" s="6" t="inlineStr"/>
       <c r="X61" s="6" t="inlineStr"/>
       <c r="Y61" s="6" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="6" t="inlineStr"/>
+      <c r="AC61" s="6" t="inlineStr"/>
+      <c r="AD61" s="6" t="inlineStr"/>
+      <c r="AE61" s="6" t="inlineStr"/>
+      <c r="AF61" s="6" t="inlineStr"/>
+      <c r="AG61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5033,6 +6045,14 @@
       <c r="W62" s="6" t="inlineStr"/>
       <c r="X62" s="6" t="inlineStr"/>
       <c r="Y62" s="6" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="6" t="inlineStr"/>
+      <c r="AC62" s="6" t="inlineStr"/>
+      <c r="AD62" s="6" t="inlineStr"/>
+      <c r="AE62" s="6" t="inlineStr"/>
+      <c r="AF62" s="6" t="inlineStr"/>
+      <c r="AG62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5082,6 +6102,14 @@
       <c r="W63" s="6" t="inlineStr"/>
       <c r="X63" s="6" t="inlineStr"/>
       <c r="Y63" s="6" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="6" t="inlineStr"/>
+      <c r="AC63" s="6" t="inlineStr"/>
+      <c r="AD63" s="6" t="inlineStr"/>
+      <c r="AE63" s="6" t="inlineStr"/>
+      <c r="AF63" s="6" t="inlineStr"/>
+      <c r="AG63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5131,6 +6159,14 @@
       <c r="W64" s="6" t="inlineStr"/>
       <c r="X64" s="6" t="inlineStr"/>
       <c r="Y64" s="6" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="6" t="inlineStr"/>
+      <c r="AC64" s="6" t="inlineStr"/>
+      <c r="AD64" s="6" t="inlineStr"/>
+      <c r="AE64" s="6" t="inlineStr"/>
+      <c r="AF64" s="6" t="inlineStr"/>
+      <c r="AG64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5180,6 +6216,14 @@
       <c r="W65" s="6" t="inlineStr"/>
       <c r="X65" s="6" t="inlineStr"/>
       <c r="Y65" s="6" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="6" t="inlineStr"/>
+      <c r="AC65" s="6" t="inlineStr"/>
+      <c r="AD65" s="6" t="inlineStr"/>
+      <c r="AE65" s="6" t="inlineStr"/>
+      <c r="AF65" s="6" t="inlineStr"/>
+      <c r="AG65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5229,6 +6273,14 @@
       <c r="W66" s="6" t="inlineStr"/>
       <c r="X66" s="6" t="inlineStr"/>
       <c r="Y66" s="6" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="6" t="inlineStr"/>
+      <c r="AC66" s="6" t="inlineStr"/>
+      <c r="AD66" s="6" t="inlineStr"/>
+      <c r="AE66" s="6" t="inlineStr"/>
+      <c r="AF66" s="6" t="inlineStr"/>
+      <c r="AG66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5310,6 +6362,18 @@
       <c r="Y67" s="6" t="n">
         <v>0.04</v>
       </c>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB67" s="6" t="inlineStr"/>
+      <c r="AC67" s="6" t="inlineStr"/>
+      <c r="AD67" s="6" t="inlineStr"/>
+      <c r="AE67" s="6" t="inlineStr"/>
+      <c r="AF67" s="6" t="inlineStr"/>
+      <c r="AG67" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5322,7 +6386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:AB67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5347,6 +6411,12 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5460,6 +6530,36 @@
           <t>ISP_OFFLOADING_AVG</t>
         </is>
       </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y1</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y2</t>
+        </is>
+      </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y3</t>
+        </is>
+      </c>
+      <c r="Z1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y1</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y2</t>
+        </is>
+      </c>
+      <c r="AB1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
@@ -5544,6 +6644,12 @@
       <c r="V2" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr"/>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+      <c r="AB2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -5580,6 +6686,12 @@
       <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr"/>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+      <c r="AB3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -5662,6 +6774,12 @@
       <c r="V4" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -5746,6 +6864,12 @@
       <c r="V5" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+      <c r="AB5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -5830,6 +6954,24 @@
       <c r="V6" s="5" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="W6" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z6" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB6" s="5" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -5913,6 +7055,24 @@
       </c>
       <c r="V7" s="5" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA7" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB7" s="5" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="8">
@@ -5993,6 +7153,24 @@
       </c>
       <c r="V8" s="5" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z8" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA8" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB8" s="5" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="9">
@@ -6030,6 +7208,12 @@
       <c r="T9" s="5" t="inlineStr"/>
       <c r="U9" s="5" t="inlineStr"/>
       <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="AA9" s="5" t="inlineStr"/>
+      <c r="AB9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -6114,6 +7298,12 @@
       <c r="V10" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="5" t="inlineStr"/>
+      <c r="AB10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -6156,6 +7346,12 @@
       <c r="T11" s="5" t="inlineStr"/>
       <c r="U11" s="5" t="inlineStr"/>
       <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="AA11" s="5" t="inlineStr"/>
+      <c r="AB11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -6240,6 +7436,12 @@
       <c r="V12" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr"/>
+      <c r="Z12" s="5" t="inlineStr"/>
+      <c r="AA12" s="5" t="inlineStr"/>
+      <c r="AB12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -6276,6 +7478,12 @@
       <c r="T13" s="5" t="inlineStr"/>
       <c r="U13" s="5" t="inlineStr"/>
       <c r="V13" s="5" t="inlineStr"/>
+      <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr"/>
+      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="AA13" s="5" t="inlineStr"/>
+      <c r="AB13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -6314,6 +7522,12 @@
       <c r="T14" s="5" t="inlineStr"/>
       <c r="U14" s="5" t="inlineStr"/>
       <c r="V14" s="5" t="inlineStr"/>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr"/>
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="5" t="inlineStr"/>
+      <c r="AB14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -6397,6 +7611,24 @@
       </c>
       <c r="V15" s="5" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z15" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="16">
@@ -6434,6 +7666,12 @@
       <c r="T16" s="5" t="inlineStr"/>
       <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr"/>
+      <c r="Z16" s="5" t="inlineStr"/>
+      <c r="AA16" s="5" t="inlineStr"/>
+      <c r="AB16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -6518,6 +7756,12 @@
       <c r="V17" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="AA17" s="5" t="inlineStr"/>
+      <c r="AB17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -6599,6 +7843,24 @@
       </c>
       <c r="V18" s="5" t="n">
         <v>0.07000000000000001</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z18" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AA18" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB18" s="5" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="19">
@@ -6642,6 +7904,12 @@
       <c r="T19" s="5" t="inlineStr"/>
       <c r="U19" s="5" t="inlineStr"/>
       <c r="V19" s="5" t="inlineStr"/>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="AA19" s="5" t="inlineStr"/>
+      <c r="AB19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6726,6 +7994,12 @@
       <c r="V20" s="5" t="n">
         <v>0.12</v>
       </c>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="Z20" s="5" t="inlineStr"/>
+      <c r="AA20" s="5" t="inlineStr"/>
+      <c r="AB20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -6810,6 +8084,12 @@
       <c r="V21" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="AA21" s="5" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -6850,6 +8130,12 @@
       <c r="T22" s="5" t="inlineStr"/>
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="5" t="inlineStr"/>
+      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="Z22" s="5" t="inlineStr"/>
+      <c r="AA22" s="5" t="inlineStr"/>
+      <c r="AB22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6930,6 +8216,24 @@
       <c r="V23" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB23" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -7010,6 +8314,24 @@
       <c r="V24" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA24" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB24" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -7094,6 +8416,12 @@
       <c r="V25" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W25" s="5" t="inlineStr"/>
+      <c r="X25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="Z25" s="5" t="inlineStr"/>
+      <c r="AA25" s="5" t="inlineStr"/>
+      <c r="AB25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -7130,6 +8458,12 @@
       <c r="T26" s="5" t="inlineStr"/>
       <c r="U26" s="5" t="inlineStr"/>
       <c r="V26" s="5" t="inlineStr"/>
+      <c r="W26" s="5" t="inlineStr"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="Z26" s="5" t="inlineStr"/>
+      <c r="AA26" s="5" t="inlineStr"/>
+      <c r="AB26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7164,6 +8498,12 @@
       <c r="T27" s="5" t="inlineStr"/>
       <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="Z27" s="5" t="inlineStr"/>
+      <c r="AA27" s="5" t="inlineStr"/>
+      <c r="AB27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -7204,6 +8544,12 @@
       <c r="T28" s="5" t="inlineStr"/>
       <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="5" t="inlineStr"/>
+      <c r="W28" s="5" t="inlineStr"/>
+      <c r="X28" s="5" t="inlineStr"/>
+      <c r="Y28" s="5" t="inlineStr"/>
+      <c r="Z28" s="5" t="inlineStr"/>
+      <c r="AA28" s="5" t="inlineStr"/>
+      <c r="AB28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -7240,6 +8586,12 @@
       <c r="T29" s="5" t="inlineStr"/>
       <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
+      <c r="W29" s="5" t="inlineStr"/>
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
+      <c r="Z29" s="5" t="inlineStr"/>
+      <c r="AA29" s="5" t="inlineStr"/>
+      <c r="AB29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -7276,6 +8628,12 @@
       <c r="T30" s="5" t="inlineStr"/>
       <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="5" t="inlineStr"/>
+      <c r="W30" s="5" t="inlineStr"/>
+      <c r="X30" s="5" t="inlineStr"/>
+      <c r="Y30" s="5" t="inlineStr"/>
+      <c r="Z30" s="5" t="inlineStr"/>
+      <c r="AA30" s="5" t="inlineStr"/>
+      <c r="AB30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -7356,6 +8714,12 @@
       <c r="V31" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W31" s="5" t="inlineStr"/>
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr"/>
+      <c r="Z31" s="5" t="inlineStr"/>
+      <c r="AA31" s="5" t="inlineStr"/>
+      <c r="AB31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -7392,6 +8756,12 @@
       <c r="T32" s="5" t="inlineStr"/>
       <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
+      <c r="W32" s="5" t="inlineStr"/>
+      <c r="X32" s="5" t="inlineStr"/>
+      <c r="Y32" s="5" t="inlineStr"/>
+      <c r="Z32" s="5" t="inlineStr"/>
+      <c r="AA32" s="5" t="inlineStr"/>
+      <c r="AB32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -7472,6 +8842,24 @@
       <c r="V33" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB33" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -7552,6 +8940,24 @@
       <c r="V34" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA34" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB34" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7632,6 +9038,24 @@
       <c r="V35" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA35" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB35" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -7714,6 +9138,12 @@
       <c r="V36" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W36" s="5" t="inlineStr"/>
+      <c r="X36" s="5" t="inlineStr"/>
+      <c r="Y36" s="5" t="inlineStr"/>
+      <c r="Z36" s="5" t="inlineStr"/>
+      <c r="AA36" s="5" t="inlineStr"/>
+      <c r="AB36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7746,6 +9176,12 @@
       <c r="T37" s="5" t="inlineStr"/>
       <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
+      <c r="W37" s="5" t="inlineStr"/>
+      <c r="X37" s="5" t="inlineStr"/>
+      <c r="Y37" s="5" t="inlineStr"/>
+      <c r="Z37" s="5" t="inlineStr"/>
+      <c r="AA37" s="5" t="inlineStr"/>
+      <c r="AB37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7782,6 +9218,12 @@
       <c r="T38" s="5" t="inlineStr"/>
       <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="5" t="inlineStr"/>
+      <c r="X38" s="5" t="inlineStr"/>
+      <c r="Y38" s="5" t="inlineStr"/>
+      <c r="Z38" s="5" t="inlineStr"/>
+      <c r="AA38" s="5" t="inlineStr"/>
+      <c r="AB38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -7860,6 +9302,24 @@
       <c r="V39" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA39" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB39" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -7938,6 +9398,24 @@
       <c r="V40" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA40" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB40" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8015,6 +9493,24 @@
       </c>
       <c r="V41" s="5" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="W41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB41" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="42">
@@ -8052,6 +9548,12 @@
       <c r="T42" s="5" t="inlineStr"/>
       <c r="U42" s="5" t="inlineStr"/>
       <c r="V42" s="5" t="inlineStr"/>
+      <c r="W42" s="5" t="inlineStr"/>
+      <c r="X42" s="5" t="inlineStr"/>
+      <c r="Y42" s="5" t="inlineStr"/>
+      <c r="Z42" s="5" t="inlineStr"/>
+      <c r="AA42" s="5" t="inlineStr"/>
+      <c r="AB42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8088,6 +9590,12 @@
       <c r="T43" s="5" t="inlineStr"/>
       <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
+      <c r="W43" s="5" t="inlineStr"/>
+      <c r="X43" s="5" t="inlineStr"/>
+      <c r="Y43" s="5" t="inlineStr"/>
+      <c r="Z43" s="5" t="inlineStr"/>
+      <c r="AA43" s="5" t="inlineStr"/>
+      <c r="AB43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8167,6 +9675,24 @@
       </c>
       <c r="V44" s="5" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="W44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA44" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB44" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="45">
@@ -8204,6 +9730,12 @@
       <c r="T45" s="5" t="inlineStr"/>
       <c r="U45" s="5" t="inlineStr"/>
       <c r="V45" s="5" t="inlineStr"/>
+      <c r="W45" s="5" t="inlineStr"/>
+      <c r="X45" s="5" t="inlineStr"/>
+      <c r="Y45" s="5" t="inlineStr"/>
+      <c r="Z45" s="5" t="inlineStr"/>
+      <c r="AA45" s="5" t="inlineStr"/>
+      <c r="AB45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -8284,6 +9816,12 @@
       <c r="V46" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W46" s="5" t="inlineStr"/>
+      <c r="X46" s="5" t="inlineStr"/>
+      <c r="Y46" s="5" t="inlineStr"/>
+      <c r="Z46" s="5" t="inlineStr"/>
+      <c r="AA46" s="5" t="inlineStr"/>
+      <c r="AB46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8363,6 +9901,24 @@
       </c>
       <c r="V47" s="5" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA47" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB47" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="48">
@@ -8400,6 +9956,12 @@
       <c r="T48" s="5" t="inlineStr"/>
       <c r="U48" s="5" t="inlineStr"/>
       <c r="V48" s="5" t="inlineStr"/>
+      <c r="W48" s="5" t="inlineStr"/>
+      <c r="X48" s="5" t="inlineStr"/>
+      <c r="Y48" s="5" t="inlineStr"/>
+      <c r="Z48" s="5" t="inlineStr"/>
+      <c r="AA48" s="5" t="inlineStr"/>
+      <c r="AB48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8484,6 +10046,12 @@
       <c r="V49" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W49" s="5" t="inlineStr"/>
+      <c r="X49" s="5" t="inlineStr"/>
+      <c r="Y49" s="5" t="inlineStr"/>
+      <c r="Z49" s="5" t="inlineStr"/>
+      <c r="AA49" s="5" t="inlineStr"/>
+      <c r="AB49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8567,6 +10135,24 @@
       </c>
       <c r="V50" s="5" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="W50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA50" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB50" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="51">
@@ -8604,6 +10190,12 @@
       <c r="T51" s="5" t="inlineStr"/>
       <c r="U51" s="5" t="inlineStr"/>
       <c r="V51" s="5" t="inlineStr"/>
+      <c r="W51" s="5" t="inlineStr"/>
+      <c r="X51" s="5" t="inlineStr"/>
+      <c r="Y51" s="5" t="inlineStr"/>
+      <c r="Z51" s="5" t="inlineStr"/>
+      <c r="AA51" s="5" t="inlineStr"/>
+      <c r="AB51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8684,6 +10276,24 @@
       <c r="V52" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA52" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB52" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8764,6 +10374,12 @@
       <c r="V53" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W53" s="5" t="inlineStr"/>
+      <c r="X53" s="5" t="inlineStr"/>
+      <c r="Y53" s="5" t="inlineStr"/>
+      <c r="Z53" s="5" t="inlineStr"/>
+      <c r="AA53" s="5" t="inlineStr"/>
+      <c r="AB53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8844,6 +10460,12 @@
       <c r="V54" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W54" s="5" t="inlineStr"/>
+      <c r="X54" s="5" t="inlineStr"/>
+      <c r="Y54" s="5" t="inlineStr"/>
+      <c r="Z54" s="5" t="inlineStr"/>
+      <c r="AA54" s="5" t="inlineStr"/>
+      <c r="AB54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8924,6 +10546,12 @@
       <c r="V55" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W55" s="5" t="inlineStr"/>
+      <c r="X55" s="5" t="inlineStr"/>
+      <c r="Y55" s="5" t="inlineStr"/>
+      <c r="Z55" s="5" t="inlineStr"/>
+      <c r="AA55" s="5" t="inlineStr"/>
+      <c r="AB55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -9004,6 +10632,24 @@
       <c r="V56" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA56" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB56" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -9084,6 +10730,24 @@
       <c r="V57" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA57" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB57" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -9164,6 +10828,24 @@
       <c r="V58" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA58" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB58" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -9243,6 +10925,24 @@
       </c>
       <c r="V59" s="5" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="W59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA59" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB59" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="60">
@@ -9280,6 +10980,12 @@
       <c r="T60" s="5" t="inlineStr"/>
       <c r="U60" s="5" t="inlineStr"/>
       <c r="V60" s="5" t="inlineStr"/>
+      <c r="W60" s="5" t="inlineStr"/>
+      <c r="X60" s="5" t="inlineStr"/>
+      <c r="Y60" s="5" t="inlineStr"/>
+      <c r="Z60" s="5" t="inlineStr"/>
+      <c r="AA60" s="5" t="inlineStr"/>
+      <c r="AB60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -9316,6 +11022,12 @@
       <c r="T61" s="5" t="inlineStr"/>
       <c r="U61" s="5" t="inlineStr"/>
       <c r="V61" s="5" t="inlineStr"/>
+      <c r="W61" s="5" t="inlineStr"/>
+      <c r="X61" s="5" t="inlineStr"/>
+      <c r="Y61" s="5" t="inlineStr"/>
+      <c r="Z61" s="5" t="inlineStr"/>
+      <c r="AA61" s="5" t="inlineStr"/>
+      <c r="AB61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -9352,6 +11064,12 @@
       <c r="T62" s="5" t="inlineStr"/>
       <c r="U62" s="5" t="inlineStr"/>
       <c r="V62" s="5" t="inlineStr"/>
+      <c r="W62" s="5" t="inlineStr"/>
+      <c r="X62" s="5" t="inlineStr"/>
+      <c r="Y62" s="5" t="inlineStr"/>
+      <c r="Z62" s="5" t="inlineStr"/>
+      <c r="AA62" s="5" t="inlineStr"/>
+      <c r="AB62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -9388,6 +11106,12 @@
       <c r="T63" s="5" t="inlineStr"/>
       <c r="U63" s="5" t="inlineStr"/>
       <c r="V63" s="5" t="inlineStr"/>
+      <c r="W63" s="5" t="inlineStr"/>
+      <c r="X63" s="5" t="inlineStr"/>
+      <c r="Y63" s="5" t="inlineStr"/>
+      <c r="Z63" s="5" t="inlineStr"/>
+      <c r="AA63" s="5" t="inlineStr"/>
+      <c r="AB63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -9424,6 +11148,12 @@
       <c r="T64" s="5" t="inlineStr"/>
       <c r="U64" s="5" t="inlineStr"/>
       <c r="V64" s="5" t="inlineStr"/>
+      <c r="W64" s="5" t="inlineStr"/>
+      <c r="X64" s="5" t="inlineStr"/>
+      <c r="Y64" s="5" t="inlineStr"/>
+      <c r="Z64" s="5" t="inlineStr"/>
+      <c r="AA64" s="5" t="inlineStr"/>
+      <c r="AB64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -9460,6 +11190,12 @@
       <c r="T65" s="5" t="inlineStr"/>
       <c r="U65" s="5" t="inlineStr"/>
       <c r="V65" s="5" t="inlineStr"/>
+      <c r="W65" s="5" t="inlineStr"/>
+      <c r="X65" s="5" t="inlineStr"/>
+      <c r="Y65" s="5" t="inlineStr"/>
+      <c r="Z65" s="5" t="inlineStr"/>
+      <c r="AA65" s="5" t="inlineStr"/>
+      <c r="AB65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -9496,6 +11232,12 @@
       <c r="T66" s="5" t="inlineStr"/>
       <c r="U66" s="5" t="inlineStr"/>
       <c r="V66" s="5" t="inlineStr"/>
+      <c r="W66" s="5" t="inlineStr"/>
+      <c r="X66" s="5" t="inlineStr"/>
+      <c r="Y66" s="5" t="inlineStr"/>
+      <c r="Z66" s="5" t="inlineStr"/>
+      <c r="AA66" s="5" t="inlineStr"/>
+      <c r="AB66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -9576,6 +11318,12 @@
       <c r="V67" s="5" t="n">
         <v>0.04</v>
       </c>
+      <c r="W67" s="5" t="inlineStr"/>
+      <c r="X67" s="5" t="inlineStr"/>
+      <c r="Y67" s="5" t="inlineStr"/>
+      <c r="Z67" s="5" t="inlineStr"/>
+      <c r="AA67" s="5" t="inlineStr"/>
+      <c r="AB67" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C67">
@@ -9818,6 +11566,78 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W67">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X67">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y67">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z67">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA67">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB67">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/VIC_curtailment.xlsx
+++ b/outputs/VIC_curtailment.xlsx
@@ -712,7 +712,7 @@
         <v>0.272</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.1812</v>
+        <v>0.1811</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>0.833539620209753</v>
@@ -981,7 +981,7 @@
         <v>0.0546</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.079</v>
+        <v>0.0789</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0.547516873654646</v>
@@ -1088,7 +1088,7 @@
         <v>0.265</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.3429</v>
+        <v>0.3422</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -1328,7 +1328,7 @@
         <v>0.2409</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.3528</v>
+        <v>0.3523</v>
       </c>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
         <v>0.1687</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.1709</v>
+        <v>0.1706</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -1674,7 +1674,7 @@
         <v>0.1136</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.1487</v>
+        <v>0.1486</v>
       </c>
       <c r="M12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -1818,7 +1818,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="n">
-        <v>0.4116</v>
+        <v>0.4111</v>
       </c>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
         <v>0.1415</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.3003</v>
+        <v>0.2998</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -2077,7 +2077,7 @@
         <v>0.2739</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.1689</v>
+        <v>0.1687</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.833539620209753</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="n">
-        <v>0.0809</v>
+        <v>0.0808</v>
       </c>
       <c r="M18" s="5" t="n">
         <v>0.390717855103594</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="n">
-        <v>0.3914</v>
+        <v>0.3908</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.389503957787889</v>
@@ -2390,7 +2390,7 @@
         <v>0.2487</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.2407</v>
+        <v>0.2404</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -2491,7 +2491,7 @@
         <v>0.0488</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.0712</v>
+        <v>0.0711</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.333698960112703</v>
@@ -2665,7 +2665,7 @@
         <v>0.2029</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0824</v>
       </c>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
@@ -3096,7 +3096,7 @@
         <v>0.099</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.1301</v>
+        <v>0.1297</v>
       </c>
       <c r="M28" s="5" t="inlineStr"/>
       <c r="N28" s="5" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
         <v>0.0762</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.2019</v>
+        <v>0.2013</v>
       </c>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
@@ -3433,7 +3433,7 @@
         <v>0.1329</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2152</v>
+        <v>0.2146</v>
       </c>
       <c r="M33" s="5" t="inlineStr"/>
       <c r="N33" s="5" t="inlineStr"/>
@@ -3542,7 +3542,7 @@
         <v>0.0488</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.0616</v>
+        <v>0.0614</v>
       </c>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3651,7 +3651,7 @@
         <v>0.0344</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.0341</v>
+        <v>0.034</v>
       </c>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="n">
-        <v>0.316</v>
+        <v>0.3157</v>
       </c>
       <c r="M36" s="5" t="n">
         <v>0.309991353939951</v>
@@ -3967,7 +3967,7 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="n">
-        <v>0.3294</v>
+        <v>0.3287</v>
       </c>
       <c r="M39" s="5" t="inlineStr"/>
       <c r="N39" s="5" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="n">
-        <v>0.3508</v>
+        <v>0.35</v>
       </c>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
@@ -4181,7 +4181,7 @@
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="5" t="inlineStr"/>
       <c r="L41" s="5" t="n">
-        <v>0.2153</v>
+        <v>0.2148</v>
       </c>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
@@ -4404,7 +4404,7 @@
         <v>0.1828</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.2574</v>
+        <v>0.2568</v>
       </c>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
@@ -4570,7 +4570,7 @@
         <v>0.1789</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.2954</v>
+        <v>0.295</v>
       </c>
       <c r="M46" s="5" t="inlineStr"/>
       <c r="N46" s="5" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
         <v>0.1393</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.2358</v>
+        <v>0.236</v>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
@@ -4829,7 +4829,7 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.0886</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>0.309110166062179</v>
@@ -5104,7 +5104,7 @@
         <v>0.0523</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.0321</v>
       </c>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>0.2792</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.1581</v>
+        <v>0.1577</v>
       </c>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="inlineStr"/>
@@ -5306,7 +5306,7 @@
         <v>0.2955</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.4217</v>
+        <v>0.4213</v>
       </c>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="inlineStr"/>
@@ -5399,7 +5399,7 @@
         <v>0.2502</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.3047</v>
+        <v>0.3039</v>
       </c>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
@@ -5492,7 +5492,7 @@
         <v>0.0793</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.1656</v>
+        <v>0.1661</v>
       </c>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="inlineStr"/>
@@ -5601,7 +5601,7 @@
         <v>0.1031</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.1504</v>
+        <v>0.1501</v>
       </c>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="inlineStr"/>
@@ -5710,7 +5710,7 @@
         <v>0.2438</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.3904</v>
+        <v>0.39</v>
       </c>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
         <v>0.1684</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.2921</v>
+        <v>0.2918</v>
       </c>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="inlineStr"/>
@@ -6582,7 +6582,7 @@
         <v>0.272</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.1812</v>
+        <v>0.1811</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.833539620209753</v>
@@ -6802,7 +6802,7 @@
         <v>0.0546</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.079</v>
+        <v>0.0789</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.547516873654646</v>
@@ -6892,7 +6892,7 @@
         <v>0.265</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3429</v>
+        <v>0.3422</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0.389503957787889</v>
@@ -7096,7 +7096,7 @@
         <v>0.2409</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3528</v>
+        <v>0.3523</v>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
@@ -7236,7 +7236,7 @@
         <v>0.1687</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.1709</v>
+        <v>0.1706</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.8554020168196</v>
@@ -7374,7 +7374,7 @@
         <v>0.1136</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1487</v>
+        <v>0.1486</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>0.827440107601162</v>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr"/>
       <c r="F14" s="5" t="n">
-        <v>0.4116</v>
+        <v>0.4111</v>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
         <v>0.1415</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3003</v>
+        <v>0.2998</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.389503957787889</v>
@@ -7694,7 +7694,7 @@
         <v>0.2739</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1689</v>
+        <v>0.1687</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.833539620209753</v>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="5" t="n">
-        <v>0.0809</v>
+        <v>0.0808</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0.390717855103594</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr"/>
       <c r="F19" s="5" t="n">
-        <v>0.3914</v>
+        <v>0.3908</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.389503957787889</v>
@@ -7932,7 +7932,7 @@
         <v>0.2487</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.2407</v>
+        <v>0.2404</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.8554020168196</v>
@@ -8022,7 +8022,7 @@
         <v>0.0488</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.0712</v>
+        <v>0.0711</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.333698960112703</v>
@@ -8158,7 +8158,7 @@
         <v>0.2029</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0824</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
@@ -8526,7 +8526,7 @@
         <v>0.099</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.1301</v>
+        <v>0.1297</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -8656,7 +8656,7 @@
         <v>0.0762</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.2019</v>
+        <v>0.2013</v>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
         <v>0.1329</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.2152</v>
+        <v>0.2146</v>
       </c>
       <c r="G33" s="5" t="inlineStr"/>
       <c r="H33" s="5" t="inlineStr"/>
@@ -8882,7 +8882,7 @@
         <v>0.0488</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0616</v>
+        <v>0.0614</v>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
@@ -8980,7 +8980,7 @@
         <v>0.0344</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.0341</v>
+        <v>0.034</v>
       </c>
       <c r="G35" s="5" t="inlineStr"/>
       <c r="H35" s="5" t="inlineStr"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="n">
-        <v>0.316</v>
+        <v>0.3157</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0.309991353939951</v>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="n">
-        <v>0.3294</v>
+        <v>0.3287</v>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="n">
-        <v>0.3508</v>
+        <v>0.35</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="n">
-        <v>0.2153</v>
+        <v>0.2148</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -9618,7 +9618,7 @@
         <v>0.1828</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.2574</v>
+        <v>0.2568</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -9758,7 +9758,7 @@
         <v>0.1789</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2954</v>
+        <v>0.295</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
@@ -9844,7 +9844,7 @@
         <v>0.1393</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.2358</v>
+        <v>0.236</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
@@ -9984,7 +9984,7 @@
         <v>0.09030000000000001</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0886</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>0.309110166062179</v>
@@ -10218,7 +10218,7 @@
         <v>0.0523</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.0323</v>
+        <v>0.0321</v>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
@@ -10316,7 +10316,7 @@
         <v>0.2792</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.1581</v>
+        <v>0.1577</v>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
@@ -10402,7 +10402,7 @@
         <v>0.2955</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.4217</v>
+        <v>0.4213</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
@@ -10488,7 +10488,7 @@
         <v>0.2502</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.3047</v>
+        <v>0.3039</v>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
@@ -10574,7 +10574,7 @@
         <v>0.0793</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.1656</v>
+        <v>0.1661</v>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
@@ -10672,7 +10672,7 @@
         <v>0.1031</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.1504</v>
+        <v>0.1501</v>
       </c>
       <c r="G57" s="5" t="inlineStr"/>
       <c r="H57" s="5" t="inlineStr"/>
@@ -10770,7 +10770,7 @@
         <v>0.2438</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.3904</v>
+        <v>0.39</v>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
@@ -11260,7 +11260,7 @@
         <v>0.1684</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.2921</v>
+        <v>0.2918</v>
       </c>
       <c r="G67" s="5" t="inlineStr"/>
       <c r="H67" s="5" t="inlineStr"/>
